--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,35 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3733562</v>
+        <v>128945971</v>
       </c>
       <c r="B2" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221447</v>
+        <v>445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Cortinarius cupreorufus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687622.3699271509</v>
+        <v>687777</v>
       </c>
       <c r="R2" t="n">
-        <v>6703635.329556052</v>
+        <v>6703507</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,31 +740,16 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Uppgiven av Tomas Troschke slutet av 1990-talet. Återfanns ej.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -775,72 +759,75 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Betad skogsmark längs väg</t>
+          <t>kalkbarrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6996375</v>
+        <v>97635191</v>
       </c>
       <c r="B3" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222361</v>
+        <v>698</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>300 m N om Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687741.0482871885</v>
+        <v>687618</v>
       </c>
       <c r="R3" t="n">
-        <v>6703553.919863001</v>
+        <v>6703661</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +852,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>C-Öst-1003</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Återupptäckt av Tomas Troschke, mycket nära den plats invid en markväg där ett exemplar sågs år 2005. Detta år blommar fältgentiana längs ett tiotal meter i den gräsbevuxna mittsträngen av vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,33 +878,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3871356</v>
+        <v>231402</v>
       </c>
       <c r="B4" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,47 +912,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221447</v>
+        <v>720</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687756.0691089551</v>
+        <v>687760</v>
       </c>
       <c r="R4" t="n">
-        <v>6703570.033886952</v>
+        <v>6703517</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,22 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,17 +990,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>betad skog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>mark</t>
+          <t>örtrik granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,22 +1007,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89165391</v>
+        <v>89165393</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1090,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687591.0271903797</v>
+        <v>687584</v>
       </c>
       <c r="R5" t="n">
-        <v>6703322.04531966</v>
+        <v>6703171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,19 +1091,9 @@
           <t>2020-10-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89165388</v>
+        <v>80770115</v>
       </c>
       <c r="B6" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,38 +1135,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>100-300 m syd Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687601.0222530449</v>
+        <v>687668</v>
       </c>
       <c r="R6" t="n">
-        <v>6703329.983754667</v>
+        <v>6703252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,22 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,31 +1209,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111733128</v>
+        <v>80770116</v>
       </c>
       <c r="B7" t="n">
-        <v>88934</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,34 +1232,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5741</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>100-300 m syd Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687588</v>
+        <v>687675</v>
       </c>
       <c r="R7" t="n">
-        <v>6703243</v>
+        <v>6703269</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,12 +1286,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,6 +1315,2913 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121432323</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>687776</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6703519</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128945974</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>687781</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6703516</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>89165399</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>687510</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6703240</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-10-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-10-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128945973</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>687775</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6703527</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111733128</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91409</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>687588</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6703243</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>89165391</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>687591</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6703322</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-10-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-10-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118536152</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14574479</v>
+      </c>
+      <c r="B15" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2010-07-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2010-07-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>60343384</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Troligen från hygge några hundra meter västerut</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14574465</v>
+      </c>
+      <c r="B17" t="n">
+        <v>43251</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102923</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Violettkantad guldvinge</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycaena hippothoe</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118536149</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58209</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118536096</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>14144885</v>
+      </c>
+      <c r="B20" t="n">
+        <v>43219</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>201028</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre tåtelsmygare</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thymelicus lineola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2009-07-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2009-07-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>14144900</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43369</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>201078</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Frejas pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Boloria freija</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Thunberg, 1791)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2009-05-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2009-05-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>14411268</v>
+      </c>
+      <c r="B22" t="n">
+        <v>43464</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>201116</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Berggräsfjäril</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lasiommata petropolitana</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2010-06-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2010-06-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>14574463</v>
+      </c>
+      <c r="B23" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6703501</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2010-07-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2010-07-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>89165388</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>687601</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6703330</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-10-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-10-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121432317</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>687770</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6703509</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3871356</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>687756</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6703570</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2005-07-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2005-07-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>betad skog</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>mark</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>87114476</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rosendal1, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>687607</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6703660</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-07-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-07-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Mittsträng på liten väg.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>87966959</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rosendal (2), Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>687778</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6703569</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C-Öst-0734</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126492808</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>300 m N om Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>687618</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6703661</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4814079</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rosendal, Gräsö, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>687760</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6703517</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2009-08-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2009-08-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Glänta i skog, betad fram till förra året</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6984068</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rosendal, 200 m NNO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>687796</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6703570</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2013-07-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2013-07-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ny lokal för loppstarr på Gräsö</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark i skog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6996375</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>687741</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6703554</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2013-07-31</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2013-07-31</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6180132</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gräsö, Rosendal (1), Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>687781</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6703580</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C-Öst-0707</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6181625</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>687797</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6703580</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,32 +1014,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89165393</v>
+        <v>135402831</v>
       </c>
       <c r="B5" t="n">
-        <v>91680</v>
+        <v>91440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>720</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,19 +1049,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687584</v>
+        <v>687766</v>
       </c>
       <c r="R5" t="n">
-        <v>6703171</v>
+        <v>6703520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,12 +1088,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Troligtvis ett mycel med ringdiameter ca 9 m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,30 +1109,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80770115</v>
+        <v>89165393</v>
       </c>
       <c r="B6" t="n">
-        <v>87309</v>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,34 +1141,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100-300 m syd Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687668</v>
+        <v>687584</v>
       </c>
       <c r="R6" t="n">
-        <v>6703252</v>
+        <v>6703171</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,12 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,19 +1224,23 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80770116</v>
+        <v>80770115</v>
       </c>
       <c r="B7" t="n">
         <v>87309</v>
@@ -1256,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687675</v>
+        <v>687668</v>
       </c>
       <c r="R7" t="n">
-        <v>6703269</v>
+        <v>6703252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,45 +1337,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121432323</v>
+        <v>80770116</v>
       </c>
       <c r="B8" t="n">
-        <v>93189</v>
+        <v>87309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>100-300 m syd Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687776</v>
+        <v>687675</v>
       </c>
       <c r="R8" t="n">
-        <v>6703519</v>
+        <v>6703269</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,12 +1402,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128945974</v>
+        <v>121432323</v>
       </c>
       <c r="B9" t="n">
         <v>93189</v>
@@ -1450,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687781</v>
+        <v>687776</v>
       </c>
       <c r="R9" t="n">
-        <v>6703516</v>
+        <v>6703519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,12 +1499,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,11 +1515,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1517,54 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89165399</v>
+        <v>128945974</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687510</v>
+        <v>687781</v>
       </c>
       <c r="R10" t="n">
-        <v>6703240</v>
+        <v>6703516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,12 +1596,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,65 +1612,75 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128945973</v>
+        <v>89165399</v>
       </c>
       <c r="B11" t="n">
-        <v>93223</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5448</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687775</v>
+        <v>687510</v>
       </c>
       <c r="R11" t="n">
-        <v>6703527</v>
+        <v>6703240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,31 +1723,30 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111733128</v>
+        <v>128945973</v>
       </c>
       <c r="B12" t="n">
-        <v>91409</v>
+        <v>93223</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,21 +1754,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5741</v>
+        <v>5448</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687588</v>
+        <v>687775</v>
       </c>
       <c r="R12" t="n">
-        <v>6703243</v>
+        <v>6703527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,12 +1808,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,6 +1824,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1826,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89165391</v>
+        <v>111733128</v>
       </c>
       <c r="B13" t="n">
-        <v>93233</v>
+        <v>91409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,43 +1856,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687591</v>
+        <v>687588</v>
       </c>
       <c r="R13" t="n">
-        <v>6703322</v>
+        <v>6703243</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,12 +1910,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,68 +1930,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118536152</v>
+        <v>89165391</v>
       </c>
       <c r="B14" t="n">
-        <v>57258</v>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100065</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687724</v>
+        <v>687591</v>
       </c>
       <c r="R14" t="n">
-        <v>6703501</v>
+        <v>6703322</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2005,12 +2016,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,52 +2036,55 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14574479</v>
+        <v>118536152</v>
       </c>
       <c r="B15" t="n">
-        <v>45049</v>
+        <v>57258</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102021</v>
+        <v>100065</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2107,12 +2121,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2139,44 +2153,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>60343384</v>
+        <v>14574479</v>
       </c>
       <c r="B16" t="n">
-        <v>57754</v>
+        <v>45049</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102118</v>
+        <v>102021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2215,27 +2223,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Troligen från hygge några hundra meter västerut</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2262,32 +2255,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14574465</v>
+        <v>60343384</v>
       </c>
       <c r="B17" t="n">
-        <v>43251</v>
+        <v>57754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102923</v>
+        <v>102118</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2295,9 +2288,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2336,12 +2331,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Troligen från hygge några hundra meter västerut</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,39 +2378,44 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118536149</v>
+        <v>14574465</v>
       </c>
       <c r="B18" t="n">
-        <v>58209</v>
+        <v>43251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102980</v>
+        <v>102923</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2437,12 +2452,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,32 +2484,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118536096</v>
+        <v>118536149</v>
       </c>
       <c r="B19" t="n">
-        <v>58439</v>
+        <v>58209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>102980</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,45 +2585,39 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14144885</v>
+        <v>118536096</v>
       </c>
       <c r="B20" t="n">
-        <v>43219</v>
+        <v>58439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>201028</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2645,12 +2654,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2661,11 +2670,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Tomt</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2682,10 +2686,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14144900</v>
+        <v>14144885</v>
       </c>
       <c r="B21" t="n">
-        <v>43369</v>
+        <v>43219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,21 +2697,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201078</v>
+        <v>201028</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Frejas pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Boloria freija</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Thunberg, 1791)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,7 +2722,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>slag-/vattenhåvning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2757,12 +2761,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2794,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14411268</v>
+        <v>14144900</v>
       </c>
       <c r="B22" t="n">
-        <v>43464</v>
+        <v>43369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,21 +2809,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>201116</v>
+        <v>201078</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Frejas pärlemorfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Boloria freija</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Thunberg, 1791)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,12 +2873,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2885,6 +2889,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2901,32 +2910,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14574463</v>
+        <v>14411268</v>
       </c>
       <c r="B23" t="n">
-        <v>43309</v>
+        <v>43464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>201146</v>
+        <v>201116</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2935,6 +2944,11 @@
           <t>imago/adult</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2971,12 +2985,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3003,52 +3017,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89165388</v>
+        <v>14574463</v>
       </c>
       <c r="B24" t="n">
-        <v>99141</v>
+        <v>43309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219862</v>
+        <v>201146</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687601</v>
+        <v>687724</v>
       </c>
       <c r="R24" t="n">
-        <v>6703330</v>
+        <v>6703501</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3072,12 +3087,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3092,61 +3107,61 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121432317</v>
+        <v>89165388</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>99141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687770</v>
+        <v>687601</v>
       </c>
       <c r="R25" t="n">
-        <v>6703509</v>
+        <v>6703330</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3173,12 +3188,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3193,22 +3208,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3871356</v>
+        <v>121432317</v>
       </c>
       <c r="B26" t="n">
-        <v>106414</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3216,47 +3235,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687756</v>
+        <v>687770</v>
       </c>
       <c r="R26" t="n">
-        <v>6703570</v>
+        <v>6703509</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3280,12 +3289,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3296,16 +3305,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>betad skog</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>mark</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3315,14 +3314,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87114476</v>
+        <v>3871356</v>
       </c>
       <c r="B27" t="n">
         <v>106414</v>
@@ -3356,22 +3355,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rosendal1, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687607</v>
+        <v>687756</v>
       </c>
       <c r="R27" t="n">
-        <v>6703660</v>
+        <v>6703570</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3395,17 +3396,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3414,13 +3410,17 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Mittsträng på liten väg.</t>
+          <t>betad skog</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>mark</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3431,17 +3431,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87966959</v>
+        <v>87114476</v>
       </c>
       <c r="B28" t="n">
-        <v>106413</v>
+        <v>106414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3472,26 +3472,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rosendal (2), Upl</t>
+          <t>Rosendal1, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687778</v>
+        <v>687607</v>
       </c>
       <c r="R28" t="n">
-        <v>6703569</v>
+        <v>6703660</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3513,24 +3509,19 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>C-Öst-0734</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
+          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3543,29 +3534,30 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Mittsträng på liten väg.</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126492808</v>
+        <v>87966959</v>
       </c>
       <c r="B29" t="n">
-        <v>106414</v>
+        <v>106413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3588,7 +3580,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3596,19 +3588,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>300 m N om Rosendal, Upl</t>
+          <t>Rosendal (2), Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687618</v>
+        <v>687778</v>
       </c>
       <c r="R29" t="n">
-        <v>6703661</v>
+        <v>6703569</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,14 +3629,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C-Öst-0734</t>
+        </is>
+      </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,60 +3662,72 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4814079</v>
+        <v>126492808</v>
       </c>
       <c r="B30" t="n">
-        <v>99879</v>
+        <v>106414</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222361</v>
+        <v>221447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rosendal, Gräsö, Upl</t>
+          <t>300 m N om Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687760</v>
+        <v>687618</v>
       </c>
       <c r="R30" t="n">
-        <v>6703517</v>
+        <v>6703661</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3733,17 +3751,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Glänta i skog, betad fram till förra året</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3752,6 +3765,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3763,14 +3777,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6984068</v>
+        <v>4814079</v>
       </c>
       <c r="B31" t="n">
         <v>99879</v>
@@ -3798,31 +3812,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rosendal, 200 m NNO om, Upl</t>
+          <t>Rosendal, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687796</v>
+        <v>687760</v>
       </c>
       <c r="R31" t="n">
-        <v>6703570</v>
+        <v>6703517</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3846,17 +3849,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ny lokal för loppstarr på Gräsö</t>
+          <t>Glänta i skog, betad fram till förra året</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,28 +3870,23 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark i skog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6996375</v>
+        <v>6984068</v>
       </c>
       <c r="B32" t="n">
         <v>99879</v>
@@ -3916,17 +3914,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal, 200 m NNO om, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687741</v>
+        <v>687796</v>
       </c>
       <c r="R32" t="n">
-        <v>6703554</v>
+        <v>6703570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3953,12 +3962,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2013-07-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ny lokal för loppstarr på Gräsö</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,70 +3983,66 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark i skog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6180132</v>
+        <v>6996375</v>
       </c>
       <c r="B33" t="n">
-        <v>106417</v>
+        <v>99879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>224210</v>
+        <v>222361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gräsö, Rosendal (1), Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687781</v>
+        <v>687741</v>
       </c>
       <c r="R33" t="n">
-        <v>6703580</v>
+        <v>6703554</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,24 +4067,14 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>C-Öst-0707</t>
-        </is>
-      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4089,23 +4089,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Floraväkterisamordn C-län</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Floraväkterisamordn C-län</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6181625</v>
+        <v>6180132</v>
       </c>
       <c r="B34" t="n">
         <v>106417</v>
@@ -4135,7 +4131,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4143,24 +4139,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Gräsö, Rosendal (1), Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687797</v>
+        <v>687781</v>
       </c>
       <c r="R34" t="n">
         <v>6703580</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4182,19 +4173,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C-Öst-0707</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,15 +4205,135 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6181625</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>687797</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6703580</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr">
+      <c r="AY35" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,32 +1014,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135402831</v>
+        <v>89165393</v>
       </c>
       <c r="B5" t="n">
-        <v>91440</v>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>720</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,19 +1049,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687766</v>
+        <v>687584</v>
       </c>
       <c r="R5" t="n">
-        <v>6703520</v>
+        <v>6703171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,17 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Troligtvis ett mycel med ringdiameter ca 9 m.</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,31 +1104,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89165393</v>
+        <v>80770115</v>
       </c>
       <c r="B6" t="n">
-        <v>91680</v>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,43 +1135,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>100-300 m syd Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687584</v>
+        <v>687668</v>
       </c>
       <c r="R6" t="n">
-        <v>6703171</v>
+        <v>6703252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,23 +1209,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80770115</v>
+        <v>80770116</v>
       </c>
       <c r="B7" t="n">
         <v>87309</v>
@@ -1275,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687668</v>
+        <v>687675</v>
       </c>
       <c r="R7" t="n">
-        <v>6703252</v>
+        <v>6703269</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,45 +1318,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80770116</v>
+        <v>121432323</v>
       </c>
       <c r="B8" t="n">
-        <v>87309</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100-300 m syd Rosendal, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687675</v>
+        <v>687776</v>
       </c>
       <c r="R8" t="n">
-        <v>6703269</v>
+        <v>6703519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,12 +1383,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,7 +1415,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121432323</v>
+        <v>128945974</v>
       </c>
       <c r="B9" t="n">
         <v>93189</v>
@@ -1469,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687776</v>
+        <v>687781</v>
       </c>
       <c r="R9" t="n">
-        <v>6703519</v>
+        <v>6703516</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,12 +1480,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,6 +1496,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1531,45 +1517,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128945974</v>
+        <v>89165399</v>
       </c>
       <c r="B10" t="n">
-        <v>93189</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687781</v>
+        <v>687510</v>
       </c>
       <c r="R10" t="n">
-        <v>6703516</v>
+        <v>6703240</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,12 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,75 +1607,65 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89165399</v>
+        <v>128945973</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>93223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>5448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687510</v>
+        <v>687775</v>
       </c>
       <c r="R11" t="n">
-        <v>6703240</v>
+        <v>6703527</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1692,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,30 +1708,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128945973</v>
+        <v>111733128</v>
       </c>
       <c r="B12" t="n">
-        <v>93223</v>
+        <v>91409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5448</v>
+        <v>5741</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687775</v>
+        <v>687588</v>
       </c>
       <c r="R12" t="n">
-        <v>6703527</v>
+        <v>6703243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,12 +1794,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,11 +1810,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1845,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111733128</v>
+        <v>89165391</v>
       </c>
       <c r="B13" t="n">
-        <v>91409</v>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,34 +1837,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687588</v>
+        <v>687591</v>
       </c>
       <c r="R13" t="n">
-        <v>6703243</v>
+        <v>6703322</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,12 +1900,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,69 +1920,68 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89165391</v>
+        <v>118536152</v>
       </c>
       <c r="B14" t="n">
-        <v>93233</v>
+        <v>57258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>100065</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687591</v>
+        <v>687724</v>
       </c>
       <c r="R14" t="n">
-        <v>6703322</v>
+        <v>6703501</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2016,12 +2005,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,55 +2025,52 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118536152</v>
+        <v>14574479</v>
       </c>
       <c r="B15" t="n">
-        <v>57258</v>
+        <v>45049</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100065</v>
+        <v>102021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2121,12 +2107,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,38 +2139,44 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14574479</v>
+        <v>60343384</v>
       </c>
       <c r="B16" t="n">
-        <v>45049</v>
+        <v>57754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102021</v>
+        <v>102118</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2223,12 +2215,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Troligen från hygge några hundra meter västerut</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,32 +2262,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>60343384</v>
+        <v>14574465</v>
       </c>
       <c r="B17" t="n">
-        <v>57754</v>
+        <v>43251</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102118</v>
+        <v>102923</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1760)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2288,11 +2295,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2331,27 +2336,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Troligen från hygge några hundra meter västerut</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,44 +2368,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14574465</v>
+        <v>118536149</v>
       </c>
       <c r="B18" t="n">
-        <v>43251</v>
+        <v>58209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102923</v>
+        <v>102980</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2452,12 +2437,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,32 +2469,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118536149</v>
+        <v>118536096</v>
       </c>
       <c r="B19" t="n">
-        <v>58209</v>
+        <v>58439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102980</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2585,39 +2570,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118536096</v>
+        <v>14144885</v>
       </c>
       <c r="B20" t="n">
-        <v>58439</v>
+        <v>43219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>201028</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2654,12 +2645,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2670,6 +2661,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2686,10 +2682,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14144885</v>
+        <v>14144900</v>
       </c>
       <c r="B21" t="n">
-        <v>43219</v>
+        <v>43369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2697,21 +2693,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201028</v>
+        <v>201078</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Frejas pärlemorfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Boloria freija</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Thunberg, 1791)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2722,7 +2718,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>slag-/vattenhåvning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2761,12 +2757,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2798,10 +2794,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14144900</v>
+        <v>14411268</v>
       </c>
       <c r="B22" t="n">
-        <v>43369</v>
+        <v>43464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,21 +2805,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>201078</v>
+        <v>201116</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Frejas pärlemorfjäril</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Boloria freija</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Thunberg, 1791)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,12 +2869,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2889,11 +2885,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Tomt</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2910,32 +2901,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14411268</v>
+        <v>14574463</v>
       </c>
       <c r="B23" t="n">
-        <v>43464</v>
+        <v>43309</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>201116</v>
+        <v>201146</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2944,11 +2935,6 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2985,12 +2971,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,53 +3003,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14574463</v>
+        <v>89165388</v>
       </c>
       <c r="B24" t="n">
-        <v>43309</v>
+        <v>99141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>201146</v>
+        <v>219862</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687724</v>
+        <v>687601</v>
       </c>
       <c r="R24" t="n">
-        <v>6703501</v>
+        <v>6703330</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3087,12 +3072,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3107,61 +3092,61 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89165388</v>
+        <v>121432317</v>
       </c>
       <c r="B25" t="n">
-        <v>99141</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219862</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687601</v>
+        <v>687770</v>
       </c>
       <c r="R25" t="n">
-        <v>6703330</v>
+        <v>6703509</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,12 +3173,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3208,26 +3193,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121432317</v>
+        <v>3871356</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>106414</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,37 +3216,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687770</v>
+        <v>687756</v>
       </c>
       <c r="R26" t="n">
-        <v>6703509</v>
+        <v>6703570</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3289,12 +3280,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3305,6 +3296,16 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>betad skog</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>mark</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3314,14 +3315,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3871356</v>
+        <v>87114476</v>
       </c>
       <c r="B27" t="n">
         <v>106414</v>
@@ -3355,24 +3356,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal1, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687756</v>
+        <v>687607</v>
       </c>
       <c r="R27" t="n">
-        <v>6703570</v>
+        <v>6703660</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3396,12 +3395,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2020-07-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3410,17 +3414,13 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>betad skog</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>mark</t>
+          <t>Mittsträng på liten väg.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3431,17 +3431,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87114476</v>
+        <v>87966959</v>
       </c>
       <c r="B28" t="n">
-        <v>106414</v>
+        <v>106413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3472,22 +3472,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rosendal1, Upl</t>
+          <t>Rosendal (2), Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687607</v>
+        <v>687778</v>
       </c>
       <c r="R28" t="n">
-        <v>6703660</v>
+        <v>6703569</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3509,19 +3513,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C-Öst-0734</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
+          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,30 +3543,29 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Mittsträng på liten väg.</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87966959</v>
+        <v>126492808</v>
       </c>
       <c r="B29" t="n">
-        <v>106413</v>
+        <v>106414</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3580,7 +3588,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3588,23 +3596,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rosendal (2), Upl</t>
+          <t>300 m N om Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687778</v>
+        <v>687618</v>
       </c>
       <c r="R29" t="n">
-        <v>6703569</v>
+        <v>6703661</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,24 +3633,14 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>C-Öst-0734</t>
-        </is>
-      </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3662,72 +3656,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126492808</v>
+        <v>4814079</v>
       </c>
       <c r="B30" t="n">
-        <v>106414</v>
+        <v>99879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221447</v>
+        <v>222361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>300 m N om Rosendal, Upl</t>
+          <t>Rosendal, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687618</v>
+        <v>687760</v>
       </c>
       <c r="R30" t="n">
-        <v>6703661</v>
+        <v>6703517</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3751,12 +3733,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2009-08-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Glänta i skog, betad fram till förra året</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,7 +3752,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3777,14 +3763,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4814079</v>
+        <v>6984068</v>
       </c>
       <c r="B31" t="n">
         <v>99879</v>
@@ -3812,20 +3798,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rosendal, Gräsö, Upl</t>
+          <t>Rosendal, 200 m NNO om, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687760</v>
+        <v>687796</v>
       </c>
       <c r="R31" t="n">
-        <v>6703517</v>
+        <v>6703570</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3849,17 +3846,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Glänta i skog, betad fram till förra året</t>
+          <t>Ny lokal för loppstarr på Gräsö</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3870,23 +3867,28 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark i skog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6984068</v>
+        <v>6996375</v>
       </c>
       <c r="B32" t="n">
         <v>99879</v>
@@ -3914,28 +3916,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rosendal, 200 m NNO om, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687796</v>
+        <v>687741</v>
       </c>
       <c r="R32" t="n">
-        <v>6703570</v>
+        <v>6703554</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,17 +3953,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ny lokal för loppstarr på Gräsö</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3983,66 +3969,70 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark i skog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6996375</v>
+        <v>6180132</v>
       </c>
       <c r="B33" t="n">
-        <v>99879</v>
+        <v>106417</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222361</v>
+        <v>224210</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Tidig fältgentiana</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Gentianella campestris var. suecica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Gräsö, Rosendal (1), Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687741</v>
+        <v>687781</v>
       </c>
       <c r="R33" t="n">
-        <v>6703554</v>
+        <v>6703580</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,14 +4057,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C-Öst-0707</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4089,19 +4089,23 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Floraväkterisamordn C-län</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Via Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6180132</v>
+        <v>6181625</v>
       </c>
       <c r="B34" t="n">
         <v>106417</v>
@@ -4131,7 +4135,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4139,19 +4143,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gräsö, Rosendal (1), Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687781</v>
+        <v>687797</v>
       </c>
       <c r="R34" t="n">
         <v>6703580</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4173,24 +4182,19 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>C-Öst-0707</t>
-        </is>
-      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4205,135 +4209,15 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Floraväkterisamordn C-län</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Floraväkterisamordn C-län</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>6181625</v>
-      </c>
-      <c r="B35" t="n">
-        <v>106417</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>224210</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tidig fältgentiana</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Gentianella campestris var. suecica</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Rosendal, Upl</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>687797</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6703580</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Gräsö</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2008-07-02</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2008-07-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Maria Pettersson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Maria Pettersson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,54 +1633,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89165399</v>
+        <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>93289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687510</v>
+        <v>687775</v>
       </c>
       <c r="R11" t="n">
-        <v>6703240</v>
+        <v>6703504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,12 +1698,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,65 +1714,75 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128945973</v>
+        <v>89165399</v>
       </c>
       <c r="B12" t="n">
-        <v>93223</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5448</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687775</v>
+        <v>687510</v>
       </c>
       <c r="R12" t="n">
-        <v>6703527</v>
+        <v>6703240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,12 +1809,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,31 +1825,30 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111733128</v>
+        <v>128945973</v>
       </c>
       <c r="B13" t="n">
-        <v>91409</v>
+        <v>93223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5741</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687588</v>
+        <v>687775</v>
       </c>
       <c r="R13" t="n">
-        <v>6703243</v>
+        <v>6703527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1926,6 +1926,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1942,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89165391</v>
+        <v>111733128</v>
       </c>
       <c r="B14" t="n">
-        <v>93233</v>
+        <v>91409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,43 +1958,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687591</v>
+        <v>687588</v>
       </c>
       <c r="R14" t="n">
-        <v>6703322</v>
+        <v>6703243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,12 +2012,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,68 +2032,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118536152</v>
+        <v>89165391</v>
       </c>
       <c r="B15" t="n">
-        <v>57258</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100065</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687724</v>
+        <v>687591</v>
       </c>
       <c r="R15" t="n">
-        <v>6703501</v>
+        <v>6703322</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2121,12 +2118,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,52 +2138,55 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14574479</v>
+        <v>118536152</v>
       </c>
       <c r="B16" t="n">
-        <v>45049</v>
+        <v>57258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102021</v>
+        <v>100065</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,44 +2255,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>60343384</v>
+        <v>14574479</v>
       </c>
       <c r="B17" t="n">
-        <v>57754</v>
+        <v>45049</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102118</v>
+        <v>102021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2331,27 +2325,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Troligen från hygge några hundra meter västerut</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,32 +2357,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14574465</v>
+        <v>60343384</v>
       </c>
       <c r="B18" t="n">
-        <v>43251</v>
+        <v>57754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102923</v>
+        <v>102118</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2411,9 +2390,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2452,12 +2433,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Troligen från hygge några hundra meter västerut</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,39 +2480,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118536149</v>
+        <v>14574465</v>
       </c>
       <c r="B19" t="n">
-        <v>58209</v>
+        <v>43251</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102980</v>
+        <v>102923</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2553,12 +2554,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2585,32 +2586,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118536096</v>
+        <v>118536149</v>
       </c>
       <c r="B20" t="n">
-        <v>58439</v>
+        <v>58209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>102980</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2686,45 +2687,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14144885</v>
+        <v>118536096</v>
       </c>
       <c r="B21" t="n">
-        <v>43219</v>
+        <v>58439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201028</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2761,12 +2756,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,11 +2772,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Tomt</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2798,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14144900</v>
+        <v>14144885</v>
       </c>
       <c r="B22" t="n">
-        <v>43369</v>
+        <v>43219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,21 +2799,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>201078</v>
+        <v>201028</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Frejas pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Boloria freija</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Thunberg, 1791)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2834,7 +2824,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>slag-/vattenhåvning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2873,12 +2863,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,10 +2900,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14411268</v>
+        <v>14144900</v>
       </c>
       <c r="B23" t="n">
-        <v>43464</v>
+        <v>43369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2921,21 +2911,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>201116</v>
+        <v>201078</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Frejas pärlemorfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Boloria freija</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Thunberg, 1791)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,12 +2975,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3001,6 +2991,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3017,32 +3012,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14574463</v>
+        <v>14411268</v>
       </c>
       <c r="B24" t="n">
-        <v>43309</v>
+        <v>43464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>201146</v>
+        <v>201116</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3051,6 +3046,11 @@
           <t>imago/adult</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,52 +3119,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89165388</v>
+        <v>14574463</v>
       </c>
       <c r="B25" t="n">
-        <v>99141</v>
+        <v>43309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219862</v>
+        <v>201146</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687601</v>
+        <v>687724</v>
       </c>
       <c r="R25" t="n">
-        <v>6703330</v>
+        <v>6703501</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3188,12 +3189,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3208,61 +3209,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121432317</v>
+        <v>89165388</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>99141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687770</v>
+        <v>687601</v>
       </c>
       <c r="R26" t="n">
-        <v>6703509</v>
+        <v>6703330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3289,12 +3290,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3309,22 +3310,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3871356</v>
+        <v>121432317</v>
       </c>
       <c r="B27" t="n">
-        <v>106414</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3332,47 +3337,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687756</v>
+        <v>687770</v>
       </c>
       <c r="R27" t="n">
-        <v>6703570</v>
+        <v>6703509</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3396,12 +3391,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3412,16 +3407,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>betad skog</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>mark</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3431,17 +3416,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87114476</v>
+        <v>135493722</v>
       </c>
       <c r="B28" t="n">
-        <v>106414</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,45 +3434,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221447</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rosendal1, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687607</v>
+        <v>687734</v>
       </c>
       <c r="R28" t="n">
-        <v>6703660</v>
+        <v>6703536</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3511,17 +3488,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3530,13 +3502,12 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Mittsträng på liten väg.</t>
+          <t>örtrik barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3554,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87966959</v>
+        <v>3871356</v>
       </c>
       <c r="B29" t="n">
-        <v>106413</v>
+        <v>106414</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3580,7 +3551,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3593,21 +3564,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rosendal (2), Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687778</v>
+        <v>687756</v>
       </c>
       <c r="R29" t="n">
-        <v>6703569</v>
+        <v>6703570</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3629,24 +3598,14 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>C-Öst-0734</t>
-        </is>
-      </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3655,30 +3614,35 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>betad skog</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>mark</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126492808</v>
+        <v>87114476</v>
       </c>
       <c r="B30" t="n">
         <v>106414</v>
@@ -3704,7 +3668,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3717,17 +3681,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>300 m N om Rosendal, Upl</t>
+          <t>Rosendal1, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687618</v>
+        <v>687607</v>
       </c>
       <c r="R30" t="n">
-        <v>6703661</v>
+        <v>6703660</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3751,12 +3715,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2020-07-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,6 +3737,11 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Mittsträng på liten väg.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3784,48 +3758,60 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4814079</v>
+        <v>87966959</v>
       </c>
       <c r="B31" t="n">
-        <v>99879</v>
+        <v>106413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222361</v>
+        <v>221447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rosendal, Gräsö, Upl</t>
+          <t>Rosendal (2), Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687760</v>
+        <v>687778</v>
       </c>
       <c r="R31" t="n">
-        <v>6703517</v>
+        <v>6703569</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3847,19 +3833,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C-Öst-0734</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Glänta i skog, betad fram till förra året</t>
+          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3868,55 +3859,56 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6984068</v>
+        <v>126492808</v>
       </c>
       <c r="B32" t="n">
-        <v>99879</v>
+        <v>106414</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222361</v>
+        <v>221447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3926,16 +3918,17 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rosendal, 200 m NNO om, Upl</t>
+          <t>300 m N om Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687796</v>
+        <v>687618</v>
       </c>
       <c r="R32" t="n">
-        <v>6703570</v>
+        <v>6703661</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,17 +3955,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ny lokal för loppstarr på Gräsö</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3981,30 +3969,26 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark i skog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6996375</v>
+        <v>4814079</v>
       </c>
       <c r="B33" t="n">
         <v>99879</v>
@@ -4035,17 +4019,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687741</v>
+        <v>687760</v>
       </c>
       <c r="R33" t="n">
-        <v>6703554</v>
+        <v>6703517</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4069,12 +4053,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2009-08-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Glänta i skog, betad fram till förra året</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,44 +4083,44 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6180132</v>
+        <v>6984068</v>
       </c>
       <c r="B34" t="n">
-        <v>106417</v>
+        <v>99879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224210</v>
+        <v>222361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4139,16 +4128,18 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gräsö, Rosendal (1), Upl</t>
+          <t>Rosendal, 200 m NNO om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687781</v>
+        <v>687796</v>
       </c>
       <c r="R34" t="n">
-        <v>6703580</v>
+        <v>6703570</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,24 +4164,19 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>C-Öst-0707</t>
-        </is>
-      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+          <t>Ny lokal för loppstarr på Gräsö</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4201,82 +4187,69 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark i skog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Floraväkterisamordn C-län</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Floraväkterisamordn C-län</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6181625</v>
+        <v>6996375</v>
       </c>
       <c r="B35" t="n">
-        <v>106417</v>
+        <v>99879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>224210</v>
+        <v>222361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687797</v>
+        <v>687741</v>
       </c>
       <c r="R35" t="n">
-        <v>6703580</v>
+        <v>6703554</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4300,17 +4273,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4325,15 +4293,251 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6180132</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gräsö, Rosendal (1), Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>687781</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6703580</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C-Öst-0707</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6181625</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>687797</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6703580</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr">
+      <c r="AY37" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945971</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97635191</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/231402</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402831</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165393</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80770115</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80770116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121432323</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945974</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493721</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165399</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128945973</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111733128</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165391</t>
         </is>
       </c>
     </row>
@@ -2252,6 +2327,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118536152</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2354,6 +2434,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14574479</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2477,6 +2562,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60343384</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2583,6 +2673,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14574465</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2684,6 +2779,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118536149</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2785,6 +2885,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118536096</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2897,6 +3002,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14144885</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3009,6 +3119,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14144900</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3116,6 +3231,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14411268</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3218,6 +3338,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14574463</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3323,6 +3448,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89165388</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3420,6 +3550,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121432317</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3522,6 +3657,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493722</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3639,6 +3779,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3871356</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3755,6 +3900,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87114476</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3879,6 +4029,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87966959</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3985,6 +4140,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126492808</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4087,6 +4247,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4814079</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4205,6 +4370,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6984068</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4302,6 +4472,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6996375</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4422,6 +4597,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6180132</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4542,8 +4722,51 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6181625</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>135402831</v>
       </c>
       <c r="B5" t="n">
-        <v>91440</v>
+        <v>91482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93289</v>
+        <v>93331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>135493722</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,32 +1034,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135402831</v>
+        <v>89165393</v>
       </c>
       <c r="B5" t="n">
-        <v>91482</v>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>720</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,19 +1069,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687766</v>
+        <v>687584</v>
       </c>
       <c r="R5" t="n">
-        <v>6703520</v>
+        <v>6703171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,17 +1108,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Troligtvis ett mycel med ringdiameter ca 9 m.</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,36 +1124,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135402831</t>
+          <t>https://artportalen.se/Sighting/89165393</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89165393</v>
+        <v>80770115</v>
       </c>
       <c r="B6" t="n">
-        <v>91680</v>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,43 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>100-300 m syd Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687584</v>
+        <v>687668</v>
       </c>
       <c r="R6" t="n">
-        <v>6703171</v>
+        <v>6703252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,28 +1234,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165393</t>
+          <t>https://artportalen.se/Sighting/80770115</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80770115</v>
+        <v>80770116</v>
       </c>
       <c r="B7" t="n">
         <v>87309</v>
@@ -1305,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687668</v>
+        <v>687675</v>
       </c>
       <c r="R7" t="n">
-        <v>6703252</v>
+        <v>6703269</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,51 +1347,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770115</t>
+          <t>https://artportalen.se/Sighting/80770116</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80770116</v>
+        <v>121432323</v>
       </c>
       <c r="B8" t="n">
-        <v>87309</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100-300 m syd Rosendal, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687675</v>
+        <v>687776</v>
       </c>
       <c r="R8" t="n">
-        <v>6703269</v>
+        <v>6703519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,12 +1418,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,13 +1449,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770116</t>
+          <t>https://artportalen.se/Sighting/121432323</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121432323</v>
+        <v>128945974</v>
       </c>
       <c r="B9" t="n">
         <v>93189</v>
@@ -1509,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687776</v>
+        <v>687781</v>
       </c>
       <c r="R9" t="n">
-        <v>6703519</v>
+        <v>6703516</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,12 +1520,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,6 +1536,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1570,16 +1556,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432323</t>
+          <t>https://artportalen.se/Sighting/128945974</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128945974</v>
+        <v>135493721</v>
       </c>
       <c r="B10" t="n">
-        <v>93189</v>
+        <v>93358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1573,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687781</v>
+        <v>687775</v>
       </c>
       <c r="R10" t="n">
-        <v>6703516</v>
+        <v>6703504</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,12 +1627,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,7 +1646,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>kalkbarrskog</t>
+          <t>örtrik barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1671,57 +1657,66 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945974</t>
+          <t>https://artportalen.se/Sighting/135493721</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135493721</v>
+        <v>89165399</v>
       </c>
       <c r="B11" t="n">
-        <v>93331</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687775</v>
+        <v>687510</v>
       </c>
       <c r="R11" t="n">
-        <v>6703504</v>
+        <v>6703240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,12 +1743,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,80 +1759,70 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>örtrik barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493721</t>
+          <t>https://artportalen.se/Sighting/89165399</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89165399</v>
+        <v>128945973</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>93223</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>5448</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687510</v>
+        <v>687775</v>
       </c>
       <c r="R12" t="n">
-        <v>6703240</v>
+        <v>6703527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,12 +1849,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,35 +1865,36 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165399</t>
+          <t>https://artportalen.se/Sighting/128945973</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128945973</v>
+        <v>111733128</v>
       </c>
       <c r="B13" t="n">
-        <v>93223</v>
+        <v>91409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,21 +1902,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5448</v>
+        <v>5741</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1940,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687775</v>
+        <v>687588</v>
       </c>
       <c r="R13" t="n">
-        <v>6703527</v>
+        <v>6703243</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,12 +1956,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,11 +1972,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2006,16 +1987,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945973</t>
+          <t>https://artportalen.se/Sighting/111733128</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111733128</v>
+        <v>89165391</v>
       </c>
       <c r="B14" t="n">
-        <v>91409</v>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,34 +2004,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687588</v>
+        <v>687591</v>
       </c>
       <c r="R14" t="n">
-        <v>6703243</v>
+        <v>6703322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,12 +2067,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,74 +2087,73 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111733128</t>
+          <t>https://artportalen.se/Sighting/89165391</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89165391</v>
+        <v>118536152</v>
       </c>
       <c r="B15" t="n">
-        <v>93233</v>
+        <v>57258</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>100065</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687591</v>
+        <v>687724</v>
       </c>
       <c r="R15" t="n">
-        <v>6703322</v>
+        <v>6703501</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,12 +2177,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,60 +2197,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165391</t>
+          <t>https://artportalen.se/Sighting/118536152</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118536152</v>
+        <v>14574479</v>
       </c>
       <c r="B16" t="n">
-        <v>57258</v>
+        <v>45049</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100065</v>
+        <v>102021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2298,12 +2284,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2329,44 +2315,50 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536152</t>
+          <t>https://artportalen.se/Sighting/14574479</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14574479</v>
+        <v>60343384</v>
       </c>
       <c r="B17" t="n">
-        <v>45049</v>
+        <v>57754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102021</v>
+        <v>102118</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2405,12 +2397,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Troligen från hygge några hundra meter västerut</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2436,38 +2443,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574479</t>
+          <t>https://artportalen.se/Sighting/60343384</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>60343384</v>
+        <v>14574465</v>
       </c>
       <c r="B18" t="n">
-        <v>57754</v>
+        <v>43251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102118</v>
+        <v>102923</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1760)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2475,11 +2482,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2518,27 +2523,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Troligen från hygge några hundra meter västerut</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,50 +2554,45 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60343384</t>
+          <t>https://artportalen.se/Sighting/14574465</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14574465</v>
+        <v>118536149</v>
       </c>
       <c r="B19" t="n">
-        <v>43251</v>
+        <v>58209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102923</v>
+        <v>102980</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2644,12 +2629,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2675,38 +2660,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574465</t>
+          <t>https://artportalen.se/Sighting/118536149</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118536149</v>
+        <v>118536096</v>
       </c>
       <c r="B20" t="n">
-        <v>58209</v>
+        <v>58439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102980</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2781,45 +2766,51 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536149</t>
+          <t>https://artportalen.se/Sighting/118536096</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118536096</v>
+        <v>14144885</v>
       </c>
       <c r="B21" t="n">
-        <v>58439</v>
+        <v>43219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103018</v>
+        <v>201028</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2856,12 +2847,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,6 +2863,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2887,16 +2883,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536096</t>
+          <t>https://artportalen.se/Sighting/14144885</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14144885</v>
+        <v>14144900</v>
       </c>
       <c r="B22" t="n">
-        <v>43219</v>
+        <v>43369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,21 +2900,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>201028</v>
+        <v>201078</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Frejas pärlemorfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Boloria freija</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Thunberg, 1791)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2929,7 +2925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>slag-/vattenhåvning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2968,12 +2964,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,16 +3000,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144885</t>
+          <t>https://artportalen.se/Sighting/14144900</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14144900</v>
+        <v>14411268</v>
       </c>
       <c r="B23" t="n">
-        <v>43369</v>
+        <v>43464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,21 +3017,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>201078</v>
+        <v>201116</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Frejas pärlemorfjäril</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Boloria freija</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Thunberg, 1791)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,12 +3081,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3101,11 +3097,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Tomt</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3121,38 +3112,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144900</t>
+          <t>https://artportalen.se/Sighting/14411268</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14411268</v>
+        <v>14574463</v>
       </c>
       <c r="B24" t="n">
-        <v>43464</v>
+        <v>43309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>201116</v>
+        <v>201146</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3161,11 +3152,6 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -3202,12 +3188,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3233,59 +3219,58 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14411268</t>
+          <t>https://artportalen.se/Sighting/14574463</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>14574463</v>
+        <v>89165388</v>
       </c>
       <c r="B25" t="n">
-        <v>43309</v>
+        <v>99141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>201146</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687724</v>
+        <v>687601</v>
       </c>
       <c r="R25" t="n">
-        <v>6703501</v>
+        <v>6703330</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3309,12 +3294,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3329,66 +3314,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574463</t>
+          <t>https://artportalen.se/Sighting/89165388</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89165388</v>
+        <v>121432317</v>
       </c>
       <c r="B26" t="n">
-        <v>99141</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219862</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687601</v>
+        <v>687770</v>
       </c>
       <c r="R26" t="n">
-        <v>6703330</v>
+        <v>6703509</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,12 +3400,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3435,31 +3420,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165388</t>
+          <t>https://artportalen.se/Sighting/121432317</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121432317</v>
+        <v>135493722</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687770</v>
+        <v>687734</v>
       </c>
       <c r="R27" t="n">
-        <v>6703509</v>
+        <v>6703536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,12 +3502,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3537,6 +3518,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3552,16 +3538,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432317</t>
+          <t>https://artportalen.se/Sighting/135493722</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135493722</v>
+        <v>3871356</v>
       </c>
       <c r="B28" t="n">
-        <v>99242</v>
+        <v>106414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,37 +3555,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687734</v>
+        <v>687756</v>
       </c>
       <c r="R28" t="n">
-        <v>6703536</v>
+        <v>6703570</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3623,12 +3619,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3642,7 +3638,12 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>örtrik barrskog</t>
+          <t>betad skog</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>mark</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3653,19 +3654,19 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493722</t>
+          <t>https://artportalen.se/Sighting/3871356</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3871356</v>
+        <v>87114476</v>
       </c>
       <c r="B29" t="n">
         <v>106414</v>
@@ -3699,24 +3700,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal1, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687756</v>
+        <v>687607</v>
       </c>
       <c r="R29" t="n">
-        <v>6703570</v>
+        <v>6703660</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3740,12 +3739,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2020-07-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3754,17 +3758,13 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>betad skog</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>mark</t>
+          <t>Mittsträng på liten väg.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3775,22 +3775,22 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3871356</t>
+          <t>https://artportalen.se/Sighting/87114476</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>87114476</v>
+        <v>87966959</v>
       </c>
       <c r="B30" t="n">
-        <v>106414</v>
+        <v>106413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3821,22 +3821,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rosendal1, Upl</t>
+          <t>Rosendal (2), Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687607</v>
+        <v>687778</v>
       </c>
       <c r="R30" t="n">
-        <v>6703660</v>
+        <v>6703569</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3858,19 +3862,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C-Öst-0734</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
+          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3883,35 +3892,34 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Mittsträng på liten väg.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87114476</t>
+          <t>https://artportalen.se/Sighting/87966959</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>87966959</v>
+        <v>126492808</v>
       </c>
       <c r="B31" t="n">
-        <v>106413</v>
+        <v>106414</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3942,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3942,23 +3950,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rosendal (2), Upl</t>
+          <t>300 m N om Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687778</v>
+        <v>687618</v>
       </c>
       <c r="R31" t="n">
-        <v>6703569</v>
+        <v>6703661</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,24 +3987,14 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>C-Öst-0734</t>
-        </is>
-      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4016,77 +4010,65 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87966959</t>
+          <t>https://artportalen.se/Sighting/126492808</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126492808</v>
+        <v>4814079</v>
       </c>
       <c r="B32" t="n">
-        <v>106414</v>
+        <v>99879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221447</v>
+        <v>222361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>300 m N om Rosendal, Upl</t>
+          <t>Rosendal, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687618</v>
+        <v>687760</v>
       </c>
       <c r="R32" t="n">
-        <v>6703661</v>
+        <v>6703517</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,12 +4092,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2009-08-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Glänta i skog, betad fram till förra året</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4124,7 +4111,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4136,19 +4122,19 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126492808</t>
+          <t>https://artportalen.se/Sighting/4814079</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4814079</v>
+        <v>6984068</v>
       </c>
       <c r="B33" t="n">
         <v>99879</v>
@@ -4176,20 +4162,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rosendal, Gräsö, Upl</t>
+          <t>Rosendal, 200 m NNO om, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687760</v>
+        <v>687796</v>
       </c>
       <c r="R33" t="n">
-        <v>6703517</v>
+        <v>6703570</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4213,17 +4210,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Glänta i skog, betad fram till förra året</t>
+          <t>Ny lokal för loppstarr på Gräsö</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,28 +4231,33 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark i skog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4814079</t>
+          <t>https://artportalen.se/Sighting/6984068</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6984068</v>
+        <v>6996375</v>
       </c>
       <c r="B34" t="n">
         <v>99879</v>
@@ -4283,28 +4285,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rosendal, 200 m NNO om, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687796</v>
+        <v>687741</v>
       </c>
       <c r="R34" t="n">
-        <v>6703570</v>
+        <v>6703554</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4331,17 +4322,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ny lokal för loppstarr på Gräsö</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4352,71 +4338,75 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark i skog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6984068</t>
+          <t>https://artportalen.se/Sighting/6996375</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6996375</v>
+        <v>6180132</v>
       </c>
       <c r="B35" t="n">
-        <v>99879</v>
+        <v>106417</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222361</v>
+        <v>224210</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Tidig fältgentiana</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Gentianella campestris var. suecica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Gräsö, Rosendal (1), Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687741</v>
+        <v>687781</v>
       </c>
       <c r="R35" t="n">
-        <v>6703554</v>
+        <v>6703580</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,14 +4431,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C-Öst-0707</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,24 +4463,28 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Floraväkterisamordn C-län</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Via Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6996375</t>
+          <t>https://artportalen.se/Sighting/6180132</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6180132</v>
+        <v>6181625</v>
       </c>
       <c r="B36" t="n">
         <v>106417</v>
@@ -4510,7 +4514,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4518,19 +4522,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gräsö, Rosendal (1), Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687781</v>
+        <v>687797</v>
       </c>
       <c r="R36" t="n">
         <v>6703580</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4552,24 +4561,19 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>C-Öst-0707</t>
-        </is>
-      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4584,145 +4588,20 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Floraväkterisamordn C-län</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Floraväkterisamordn C-län</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/6180132</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>6181625</v>
-      </c>
-      <c r="B37" t="n">
-        <v>106417</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>224210</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tidig fältgentiana</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Gentianella campestris var. suecica</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Rosendal, Upl</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>687797</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6703580</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Gräsö</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2008-07-02</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2008-07-02</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Maria Pettersson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Maria Pettersson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
-      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6181625</t>
         </is>
@@ -4765,7 +4644,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,32 +1034,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89165393</v>
+        <v>135402831</v>
       </c>
       <c r="B5" t="n">
-        <v>91680</v>
+        <v>91509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>720</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,19 +1069,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687584</v>
+        <v>687766</v>
       </c>
       <c r="R5" t="n">
-        <v>6703171</v>
+        <v>6703520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,12 +1108,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Troligtvis ett mycel med ringdiameter ca 9 m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,35 +1129,36 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165393</t>
+          <t>https://artportalen.se/Sighting/135402831</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80770115</v>
+        <v>89165393</v>
       </c>
       <c r="B6" t="n">
-        <v>87309</v>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1166,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100-300 m syd Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687668</v>
+        <v>687584</v>
       </c>
       <c r="R6" t="n">
-        <v>6703252</v>
+        <v>6703171</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1229,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,24 +1249,28 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770115</t>
+          <t>https://artportalen.se/Sighting/89165393</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80770116</v>
+        <v>80770115</v>
       </c>
       <c r="B7" t="n">
         <v>87309</v>
@@ -1286,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687675</v>
+        <v>687668</v>
       </c>
       <c r="R7" t="n">
-        <v>6703269</v>
+        <v>6703252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,51 +1366,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770116</t>
+          <t>https://artportalen.se/Sighting/80770115</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121432323</v>
+        <v>80770116</v>
       </c>
       <c r="B8" t="n">
-        <v>93189</v>
+        <v>87309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>100-300 m syd Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687776</v>
+        <v>687675</v>
       </c>
       <c r="R8" t="n">
-        <v>6703519</v>
+        <v>6703269</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,12 +1437,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,13 +1468,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432323</t>
+          <t>https://artportalen.se/Sighting/80770116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128945974</v>
+        <v>121432323</v>
       </c>
       <c r="B9" t="n">
         <v>93189</v>
@@ -1490,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687781</v>
+        <v>687776</v>
       </c>
       <c r="R9" t="n">
-        <v>6703516</v>
+        <v>6703519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,12 +1539,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,11 +1555,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1556,16 +1570,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945974</t>
+          <t>https://artportalen.se/Sighting/121432323</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135493721</v>
+        <v>128945974</v>
       </c>
       <c r="B10" t="n">
-        <v>93358</v>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687775</v>
+        <v>687781</v>
       </c>
       <c r="R10" t="n">
-        <v>6703504</v>
+        <v>6703516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,12 +1641,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,7 +1660,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>örtrik barrskog</t>
+          <t>kalkbarrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1657,66 +1671,57 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493721</t>
+          <t>https://artportalen.se/Sighting/128945974</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89165399</v>
+        <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>93358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687510</v>
+        <v>687775</v>
       </c>
       <c r="R11" t="n">
-        <v>6703240</v>
+        <v>6703504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,70 +1764,80 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165399</t>
+          <t>https://artportalen.se/Sighting/135493721</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128945973</v>
+        <v>89165399</v>
       </c>
       <c r="B12" t="n">
-        <v>93223</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5448</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687775</v>
+        <v>687510</v>
       </c>
       <c r="R12" t="n">
-        <v>6703527</v>
+        <v>6703240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,12 +1864,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,36 +1880,35 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945973</t>
+          <t>https://artportalen.se/Sighting/89165399</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111733128</v>
+        <v>128945973</v>
       </c>
       <c r="B13" t="n">
-        <v>91409</v>
+        <v>93223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,21 +1916,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5741</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1926,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687588</v>
+        <v>687775</v>
       </c>
       <c r="R13" t="n">
-        <v>6703243</v>
+        <v>6703527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,12 +1970,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,6 +1986,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1987,16 +2006,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111733128</t>
+          <t>https://artportalen.se/Sighting/128945973</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89165391</v>
+        <v>111733128</v>
       </c>
       <c r="B14" t="n">
-        <v>93233</v>
+        <v>91409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,43 +2023,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687591</v>
+        <v>687588</v>
       </c>
       <c r="R14" t="n">
-        <v>6703322</v>
+        <v>6703243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,12 +2077,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2087,73 +2097,74 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165391</t>
+          <t>https://artportalen.se/Sighting/111733128</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118536152</v>
+        <v>89165391</v>
       </c>
       <c r="B15" t="n">
-        <v>57258</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100065</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687724</v>
+        <v>687591</v>
       </c>
       <c r="R15" t="n">
-        <v>6703501</v>
+        <v>6703322</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2177,12 +2188,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,57 +2208,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536152</t>
+          <t>https://artportalen.se/Sighting/89165391</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14574479</v>
+        <v>118536152</v>
       </c>
       <c r="B16" t="n">
-        <v>45049</v>
+        <v>57258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102021</v>
+        <v>100065</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2284,12 +2298,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,50 +2329,44 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574479</t>
+          <t>https://artportalen.se/Sighting/118536152</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>60343384</v>
+        <v>14574479</v>
       </c>
       <c r="B17" t="n">
-        <v>57754</v>
+        <v>45049</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102118</v>
+        <v>102021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2397,27 +2405,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Troligen från hygge några hundra meter västerut</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,38 +2436,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60343384</t>
+          <t>https://artportalen.se/Sighting/14574479</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14574465</v>
+        <v>60343384</v>
       </c>
       <c r="B18" t="n">
-        <v>43251</v>
+        <v>57754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102923</v>
+        <v>102118</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2482,9 +2475,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2523,12 +2518,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Troligen från hygge några hundra meter västerut</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,45 +2564,50 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574465</t>
+          <t>https://artportalen.se/Sighting/60343384</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118536149</v>
+        <v>14574465</v>
       </c>
       <c r="B19" t="n">
-        <v>58209</v>
+        <v>43251</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102980</v>
+        <v>102923</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2629,12 +2644,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,38 +2675,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536149</t>
+          <t>https://artportalen.se/Sighting/14574465</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118536096</v>
+        <v>118536149</v>
       </c>
       <c r="B20" t="n">
-        <v>58439</v>
+        <v>58209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>102980</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2766,51 +2781,45 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536096</t>
+          <t>https://artportalen.se/Sighting/118536149</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14144885</v>
+        <v>118536096</v>
       </c>
       <c r="B21" t="n">
-        <v>43219</v>
+        <v>58439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201028</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2847,12 +2856,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,11 +2872,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Tomt</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2883,16 +2887,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144885</t>
+          <t>https://artportalen.se/Sighting/118536096</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14144900</v>
+        <v>14144885</v>
       </c>
       <c r="B22" t="n">
-        <v>43369</v>
+        <v>43219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2900,21 +2904,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>201078</v>
+        <v>201028</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Frejas pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Boloria freija</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Thunberg, 1791)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,7 +2929,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>slag-/vattenhåvning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2964,12 +2968,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,16 +3004,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144900</t>
+          <t>https://artportalen.se/Sighting/14144885</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14411268</v>
+        <v>14144900</v>
       </c>
       <c r="B23" t="n">
-        <v>43464</v>
+        <v>43369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,21 +3021,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>201116</v>
+        <v>201078</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Frejas pärlemorfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Boloria freija</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Thunberg, 1791)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,12 +3085,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,6 +3101,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3112,38 +3121,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14411268</t>
+          <t>https://artportalen.se/Sighting/14144900</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14574463</v>
+        <v>14411268</v>
       </c>
       <c r="B24" t="n">
-        <v>43309</v>
+        <v>43464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>201146</v>
+        <v>201116</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3152,6 +3161,11 @@
           <t>imago/adult</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -3188,12 +3202,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3219,58 +3233,59 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574463</t>
+          <t>https://artportalen.se/Sighting/14411268</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89165388</v>
+        <v>14574463</v>
       </c>
       <c r="B25" t="n">
-        <v>99141</v>
+        <v>43309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219862</v>
+        <v>201146</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687601</v>
+        <v>687724</v>
       </c>
       <c r="R25" t="n">
-        <v>6703330</v>
+        <v>6703501</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3294,12 +3309,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3314,66 +3329,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165388</t>
+          <t>https://artportalen.se/Sighting/14574463</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121432317</v>
+        <v>89165388</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>99141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687770</v>
+        <v>687601</v>
       </c>
       <c r="R26" t="n">
-        <v>6703509</v>
+        <v>6703330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,12 +3415,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,27 +3435,31 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432317</t>
+          <t>https://artportalen.se/Sighting/89165388</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135493722</v>
+        <v>121432317</v>
       </c>
       <c r="B27" t="n">
-        <v>99269</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,10 +3491,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687734</v>
+        <v>687770</v>
       </c>
       <c r="R27" t="n">
-        <v>6703536</v>
+        <v>6703509</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3502,12 +3521,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3518,11 +3537,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>örtrik barrskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3538,16 +3552,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493722</t>
+          <t>https://artportalen.se/Sighting/121432317</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3871356</v>
+        <v>135493722</v>
       </c>
       <c r="B28" t="n">
-        <v>106414</v>
+        <v>99269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,47 +3569,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221447</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687756</v>
+        <v>687734</v>
       </c>
       <c r="R28" t="n">
-        <v>6703570</v>
+        <v>6703536</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,12 +3623,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,12 +3642,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>betad skog</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>mark</t>
+          <t>örtrik barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3654,19 +3653,19 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3871356</t>
+          <t>https://artportalen.se/Sighting/135493722</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87114476</v>
+        <v>3871356</v>
       </c>
       <c r="B29" t="n">
         <v>106414</v>
@@ -3700,22 +3699,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rosendal1, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687607</v>
+        <v>687756</v>
       </c>
       <c r="R29" t="n">
-        <v>6703660</v>
+        <v>6703570</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3739,17 +3740,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3758,13 +3754,17 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Mittsträng på liten väg.</t>
+          <t>betad skog</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>mark</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3775,22 +3775,22 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87114476</t>
+          <t>https://artportalen.se/Sighting/3871356</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>87966959</v>
+        <v>87114476</v>
       </c>
       <c r="B30" t="n">
-        <v>106413</v>
+        <v>106414</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3821,26 +3821,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rosendal (2), Upl</t>
+          <t>Rosendal1, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687778</v>
+        <v>687607</v>
       </c>
       <c r="R30" t="n">
-        <v>6703569</v>
+        <v>6703660</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3862,24 +3858,19 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>C-Öst-0734</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
+          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3892,34 +3883,35 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Mittsträng på liten väg.</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87966959</t>
+          <t>https://artportalen.se/Sighting/87114476</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126492808</v>
+        <v>87966959</v>
       </c>
       <c r="B31" t="n">
-        <v>106414</v>
+        <v>106413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3934,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3950,19 +3942,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>300 m N om Rosendal, Upl</t>
+          <t>Rosendal (2), Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687618</v>
+        <v>687778</v>
       </c>
       <c r="R31" t="n">
-        <v>6703661</v>
+        <v>6703569</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3987,14 +3983,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C-Öst-0734</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4010,65 +4016,77 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126492808</t>
+          <t>https://artportalen.se/Sighting/87966959</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4814079</v>
+        <v>126492808</v>
       </c>
       <c r="B32" t="n">
-        <v>99879</v>
+        <v>106414</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222361</v>
+        <v>221447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rosendal, Gräsö, Upl</t>
+          <t>300 m N om Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687760</v>
+        <v>687618</v>
       </c>
       <c r="R32" t="n">
-        <v>6703517</v>
+        <v>6703661</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4092,17 +4110,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Glänta i skog, betad fram till förra året</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4111,6 +4124,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4122,19 +4136,19 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4814079</t>
+          <t>https://artportalen.se/Sighting/126492808</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6984068</v>
+        <v>4814079</v>
       </c>
       <c r="B33" t="n">
         <v>99879</v>
@@ -4162,31 +4176,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rosendal, 200 m NNO om, Upl</t>
+          <t>Rosendal, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687796</v>
+        <v>687760</v>
       </c>
       <c r="R33" t="n">
-        <v>6703570</v>
+        <v>6703517</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4210,17 +4213,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ny lokal för loppstarr på Gräsö</t>
+          <t>Glänta i skog, betad fram till förra året</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4231,33 +4234,28 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark i skog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6984068</t>
+          <t>https://artportalen.se/Sighting/4814079</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6996375</v>
+        <v>6984068</v>
       </c>
       <c r="B34" t="n">
         <v>99879</v>
@@ -4285,17 +4283,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal, 200 m NNO om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687741</v>
+        <v>687796</v>
       </c>
       <c r="R34" t="n">
-        <v>6703554</v>
+        <v>6703570</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4322,12 +4331,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2013-07-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ny lokal för loppstarr på Gräsö</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4338,75 +4352,71 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark i skog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6996375</t>
+          <t>https://artportalen.se/Sighting/6984068</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6180132</v>
+        <v>6996375</v>
       </c>
       <c r="B35" t="n">
-        <v>106417</v>
+        <v>99879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>224210</v>
+        <v>222361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gräsö, Rosendal (1), Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687781</v>
+        <v>687741</v>
       </c>
       <c r="R35" t="n">
-        <v>6703580</v>
+        <v>6703554</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4431,24 +4441,14 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>C-Öst-0707</t>
-        </is>
-      </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,28 +4463,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Floraväkterisamordn C-län</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Via Floraväkterisamordn C-län</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6180132</t>
+          <t>https://artportalen.se/Sighting/6996375</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6181625</v>
+        <v>6180132</v>
       </c>
       <c r="B36" t="n">
         <v>106417</v>
@@ -4514,7 +4510,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4522,24 +4518,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Gräsö, Rosendal (1), Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687797</v>
+        <v>687781</v>
       </c>
       <c r="R36" t="n">
         <v>6703580</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4561,19 +4552,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C-Öst-0707</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,20 +4584,145 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6180132</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6181625</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>687797</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6703580</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr">
+      <c r="AY37" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6181625</t>
         </is>
@@ -4644,6 +4765,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,32 +1034,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89165393</v>
+        <v>135402831</v>
       </c>
       <c r="B5" t="n">
-        <v>91680</v>
+        <v>91512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>720</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,19 +1069,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687584</v>
+        <v>687766</v>
       </c>
       <c r="R5" t="n">
-        <v>6703171</v>
+        <v>6703520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,12 +1108,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Troligtvis ett mycel med ringdiameter ca 9 m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,35 +1129,36 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165393</t>
+          <t>https://artportalen.se/Sighting/135402831</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80770115</v>
+        <v>89165393</v>
       </c>
       <c r="B6" t="n">
-        <v>87309</v>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1166,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100-300 m syd Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687668</v>
+        <v>687584</v>
       </c>
       <c r="R6" t="n">
-        <v>6703252</v>
+        <v>6703171</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1229,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,24 +1249,28 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770115</t>
+          <t>https://artportalen.se/Sighting/89165393</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80770116</v>
+        <v>80770115</v>
       </c>
       <c r="B7" t="n">
         <v>87309</v>
@@ -1286,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687675</v>
+        <v>687668</v>
       </c>
       <c r="R7" t="n">
-        <v>6703269</v>
+        <v>6703252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,51 +1366,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770116</t>
+          <t>https://artportalen.se/Sighting/80770115</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121432323</v>
+        <v>80770116</v>
       </c>
       <c r="B8" t="n">
-        <v>93189</v>
+        <v>87309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>100-300 m syd Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687776</v>
+        <v>687675</v>
       </c>
       <c r="R8" t="n">
-        <v>6703519</v>
+        <v>6703269</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,12 +1437,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,13 +1468,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432323</t>
+          <t>https://artportalen.se/Sighting/80770116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128945974</v>
+        <v>121432323</v>
       </c>
       <c r="B9" t="n">
         <v>93189</v>
@@ -1490,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687781</v>
+        <v>687776</v>
       </c>
       <c r="R9" t="n">
-        <v>6703516</v>
+        <v>6703519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,12 +1539,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,11 +1555,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1556,60 +1570,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945974</t>
+          <t>https://artportalen.se/Sighting/121432323</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89165399</v>
+        <v>128945974</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687510</v>
+        <v>687781</v>
       </c>
       <c r="R10" t="n">
-        <v>6703240</v>
+        <v>6703516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,12 +1641,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,35 +1657,36 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165399</t>
+          <t>https://artportalen.se/Sighting/128945974</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128945973</v>
+        <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93223</v>
+        <v>93363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5448</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,7 +1721,7 @@
         <v>687775</v>
       </c>
       <c r="R11" t="n">
-        <v>6703527</v>
+        <v>6703504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,7 +1767,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>kalkbarrskog</t>
+          <t>örtrik barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1772,57 +1778,66 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945973</t>
+          <t>https://artportalen.se/Sighting/135493721</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111733128</v>
+        <v>89165399</v>
       </c>
       <c r="B12" t="n">
-        <v>91409</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5741</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687588</v>
+        <v>687510</v>
       </c>
       <c r="R12" t="n">
-        <v>6703243</v>
+        <v>6703240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,12 +1864,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,27 +1884,31 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111733128</t>
+          <t>https://artportalen.se/Sighting/89165399</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89165391</v>
+        <v>128945973</v>
       </c>
       <c r="B13" t="n">
-        <v>93233</v>
+        <v>93223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,43 +1916,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687591</v>
+        <v>687775</v>
       </c>
       <c r="R13" t="n">
-        <v>6703322</v>
+        <v>6703527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,12 +1970,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1976,77 +1986,74 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165391</t>
+          <t>https://artportalen.se/Sighting/128945973</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118536152</v>
+        <v>111733128</v>
       </c>
       <c r="B14" t="n">
-        <v>57258</v>
+        <v>91409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100065</v>
+        <v>5741</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687724</v>
+        <v>687588</v>
       </c>
       <c r="R14" t="n">
-        <v>6703501</v>
+        <v>6703243</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2070,12 +2077,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,59 +2108,63 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536152</t>
+          <t>https://artportalen.se/Sighting/111733128</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14574479</v>
+        <v>89165391</v>
       </c>
       <c r="B15" t="n">
-        <v>45049</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102021</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687724</v>
+        <v>687591</v>
       </c>
       <c r="R15" t="n">
-        <v>6703501</v>
+        <v>6703322</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2177,12 +2188,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,27 +2208,31 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574479</t>
+          <t>https://artportalen.se/Sighting/89165391</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>60343384</v>
+        <v>118536152</v>
       </c>
       <c r="B16" t="n">
-        <v>57754</v>
+        <v>57258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,35 +2240,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102118</v>
+        <v>100065</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2290,27 +2298,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Troligen från hygge några hundra meter västerut</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,16 +2329,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60343384</t>
+          <t>https://artportalen.se/Sighting/118536152</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14574465</v>
+        <v>14574479</v>
       </c>
       <c r="B17" t="n">
-        <v>43251</v>
+        <v>45049</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,28 +2346,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102923</v>
+        <v>102021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -2416,12 +2405,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,33 +2436,33 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574465</t>
+          <t>https://artportalen.se/Sighting/14574479</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118536149</v>
+        <v>60343384</v>
       </c>
       <c r="B18" t="n">
-        <v>58209</v>
+        <v>57754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102980</v>
+        <v>102118</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2481,11 +2470,18 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2522,12 +2518,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Troligen från hygge några hundra meter västerut</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,45 +2564,50 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536149</t>
+          <t>https://artportalen.se/Sighting/60343384</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118536096</v>
+        <v>14574465</v>
       </c>
       <c r="B19" t="n">
-        <v>58439</v>
+        <v>43251</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>102923</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2628,12 +2644,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,16 +2675,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536096</t>
+          <t>https://artportalen.se/Sighting/14574465</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14144885</v>
+        <v>118536149</v>
       </c>
       <c r="B20" t="n">
-        <v>43219</v>
+        <v>58209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,34 +2692,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>201028</v>
+        <v>102980</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2740,12 +2750,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,11 +2766,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Tomt</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2776,51 +2781,45 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144885</t>
+          <t>https://artportalen.se/Sighting/118536149</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14144900</v>
+        <v>118536096</v>
       </c>
       <c r="B21" t="n">
-        <v>43369</v>
+        <v>58439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201078</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Frejas pärlemorfjäril</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Boloria freija</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Thunberg, 1791)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2857,12 +2856,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,11 +2872,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Tomt</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2893,16 +2887,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144900</t>
+          <t>https://artportalen.se/Sighting/118536096</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14411268</v>
+        <v>14144885</v>
       </c>
       <c r="B22" t="n">
-        <v>43464</v>
+        <v>43219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,21 +2904,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>201116</v>
+        <v>201028</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2935,7 +2929,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>slag-/vattenhåvning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2974,12 +2968,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,6 +2984,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3005,38 +3004,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14411268</t>
+          <t>https://artportalen.se/Sighting/14144885</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14574463</v>
+        <v>14144900</v>
       </c>
       <c r="B23" t="n">
-        <v>43309</v>
+        <v>43369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>201146</v>
+        <v>201078</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Frejas pärlemorfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Boloria freija</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Thunberg, 1791)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3045,6 +3044,11 @@
           <t>imago/adult</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -3081,12 +3085,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,6 +3101,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3112,58 +3121,64 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574463</t>
+          <t>https://artportalen.se/Sighting/14144900</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89165388</v>
+        <v>14411268</v>
       </c>
       <c r="B24" t="n">
-        <v>99141</v>
+        <v>43464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219862</v>
+        <v>201116</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687601</v>
+        <v>687724</v>
       </c>
       <c r="R24" t="n">
-        <v>6703330</v>
+        <v>6703501</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3187,12 +3202,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3207,31 +3222,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165388</t>
+          <t>https://artportalen.se/Sighting/14411268</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121432317</v>
+        <v>14574463</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>43309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,37 +3250,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>201146</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687770</v>
+        <v>687724</v>
       </c>
       <c r="R25" t="n">
-        <v>6703509</v>
+        <v>6703501</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3293,12 +3309,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3324,64 +3340,58 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432317</t>
+          <t>https://artportalen.se/Sighting/14574463</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3871356</v>
+        <v>89165388</v>
       </c>
       <c r="B26" t="n">
-        <v>106414</v>
+        <v>99141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221447</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687756</v>
+        <v>687601</v>
       </c>
       <c r="R26" t="n">
-        <v>6703570</v>
+        <v>6703330</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3405,12 +3415,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3421,41 +3431,35 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>betad skog</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>mark</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3871356</t>
+          <t>https://artportalen.se/Sighting/89165388</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87114476</v>
+        <v>121432317</v>
       </c>
       <c r="B27" t="n">
-        <v>106414</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3463,45 +3467,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rosendal1, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687607</v>
+        <v>687770</v>
       </c>
       <c r="R27" t="n">
-        <v>6703660</v>
+        <v>6703509</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,17 +3521,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,14 +3535,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Mittsträng på liten väg.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3567,16 +3552,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87114476</t>
+          <t>https://artportalen.se/Sighting/121432317</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87966959</v>
+        <v>135493722</v>
       </c>
       <c r="B28" t="n">
-        <v>106413</v>
+        <v>99274</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3584,46 +3569,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221447</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rosendal (2), Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687778</v>
+        <v>687734</v>
       </c>
       <c r="R28" t="n">
-        <v>6703569</v>
+        <v>6703536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3648,24 +3621,14 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>C-Öst-0734</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3674,38 +3637,38 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87966959</t>
+          <t>https://artportalen.se/Sighting/135493722</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126492808</v>
+        <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>106414</v>
+        <v>99274</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3713,45 +3676,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221447</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>300 m N om Rosendal, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687618</v>
+        <v>687766</v>
       </c>
       <c r="R29" t="n">
-        <v>6703661</v>
+        <v>6703514</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,12 +3730,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3789,7 +3744,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3807,54 +3761,64 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126492808</t>
+          <t>https://artportalen.se/Sighting/135777737</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4814079</v>
+        <v>3871356</v>
       </c>
       <c r="B30" t="n">
-        <v>99879</v>
+        <v>106414</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222361</v>
+        <v>221447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rosendal, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687760</v>
+        <v>687756</v>
       </c>
       <c r="R30" t="n">
-        <v>6703517</v>
+        <v>6703570</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3878,17 +3842,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Glänta i skog, betad fram till förra året</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3899,6 +3858,16 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>betad skog</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>mark</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3914,43 +3883,39 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4814079</t>
+          <t>https://artportalen.se/Sighting/3871356</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6984068</v>
+        <v>87114476</v>
       </c>
       <c r="B31" t="n">
-        <v>99879</v>
+        <v>106414</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222361</v>
+        <v>221447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3960,19 +3925,20 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rosendal, 200 m NNO om, Upl</t>
+          <t>Rosendal1, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687796</v>
+        <v>687607</v>
       </c>
       <c r="R31" t="n">
-        <v>6703570</v>
+        <v>6703660</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3996,17 +3962,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ny lokal för loppstarr på Gräsö</t>
+          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4015,73 +3981,86 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Fuktig ängsmark i skog</t>
+          <t>Mittsträng på liten väg.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6984068</t>
+          <t>https://artportalen.se/Sighting/87114476</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6996375</v>
+        <v>87966959</v>
       </c>
       <c r="B32" t="n">
-        <v>99879</v>
+        <v>106413</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222361</v>
+        <v>221447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal (2), Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687741</v>
+        <v>687778</v>
       </c>
       <c r="R32" t="n">
-        <v>6703554</v>
+        <v>6703569</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4106,14 +4085,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C-Öst-0734</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,33 +4111,38 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6996375</t>
+          <t>https://artportalen.se/Sighting/87966959</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6180132</v>
+        <v>126492808</v>
       </c>
       <c r="B33" t="n">
-        <v>106417</v>
+        <v>106414</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,26 +4150,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>224210</v>
+        <v>221447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4183,16 +4173,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gräsö, Rosendal (1), Upl</t>
+          <t>300 m N om Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687781</v>
+        <v>687618</v>
       </c>
       <c r="R33" t="n">
-        <v>6703580</v>
+        <v>6703661</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4217,24 +4210,14 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>C-Öst-0707</t>
-        </is>
-      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4243,89 +4226,72 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Floraväkterisamordn C-län</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Floraväkterisamordn C-län</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6180132</t>
+          <t>https://artportalen.se/Sighting/126492808</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6181625</v>
+        <v>4814079</v>
       </c>
       <c r="B34" t="n">
-        <v>106417</v>
+        <v>99879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224210</v>
+        <v>222361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687797</v>
+        <v>687760</v>
       </c>
       <c r="R34" t="n">
-        <v>6703580</v>
+        <v>6703517</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4349,17 +4315,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+          <t>Glänta i skog, betad fram till förra året</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4374,20 +4340,491 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4814079</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6984068</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rosendal, 200 m NNO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>687796</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6703570</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2013-07-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2013-07-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ny lokal för loppstarr på Gräsö</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark i skog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6984068</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6996375</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>687741</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6703554</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2013-07-31</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2013-07-31</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6996375</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6180132</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gräsö, Rosendal (1), Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>687781</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6703580</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C-Öst-0707</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6180132</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6181625</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>687797</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6703580</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6181625</t>
         </is>
@@ -4428,6 +4865,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>135402831</v>
       </c>
       <c r="B5" t="n">
-        <v>91512</v>
+        <v>91514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93363</v>
+        <v>93365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>135493722</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,32 +1034,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135402831</v>
+        <v>89165393</v>
       </c>
       <c r="B5" t="n">
-        <v>91514</v>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>720</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,19 +1069,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687766</v>
+        <v>687584</v>
       </c>
       <c r="R5" t="n">
-        <v>6703520</v>
+        <v>6703171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,17 +1108,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Troligtvis ett mycel med ringdiameter ca 9 m.</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,36 +1124,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135402831</t>
+          <t>https://artportalen.se/Sighting/89165393</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89165393</v>
+        <v>80770115</v>
       </c>
       <c r="B6" t="n">
-        <v>91680</v>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,43 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>100-300 m syd Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687584</v>
+        <v>687668</v>
       </c>
       <c r="R6" t="n">
-        <v>6703171</v>
+        <v>6703252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,28 +1234,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165393</t>
+          <t>https://artportalen.se/Sighting/80770115</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80770115</v>
+        <v>80770116</v>
       </c>
       <c r="B7" t="n">
         <v>87309</v>
@@ -1305,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687668</v>
+        <v>687675</v>
       </c>
       <c r="R7" t="n">
-        <v>6703252</v>
+        <v>6703269</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,51 +1347,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770115</t>
+          <t>https://artportalen.se/Sighting/80770116</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80770116</v>
+        <v>121432323</v>
       </c>
       <c r="B8" t="n">
-        <v>87309</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100-300 m syd Rosendal, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687675</v>
+        <v>687776</v>
       </c>
       <c r="R8" t="n">
-        <v>6703269</v>
+        <v>6703519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,12 +1418,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,13 +1449,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770116</t>
+          <t>https://artportalen.se/Sighting/121432323</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121432323</v>
+        <v>128945974</v>
       </c>
       <c r="B9" t="n">
         <v>93189</v>
@@ -1509,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687776</v>
+        <v>687781</v>
       </c>
       <c r="R9" t="n">
-        <v>6703519</v>
+        <v>6703516</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,12 +1520,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,6 +1536,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1570,16 +1556,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432323</t>
+          <t>https://artportalen.se/Sighting/128945974</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128945974</v>
+        <v>135493721</v>
       </c>
       <c r="B10" t="n">
-        <v>93189</v>
+        <v>93365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1573,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687781</v>
+        <v>687775</v>
       </c>
       <c r="R10" t="n">
-        <v>6703516</v>
+        <v>6703504</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,12 +1627,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,7 +1646,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>kalkbarrskog</t>
+          <t>örtrik barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1671,57 +1657,66 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945974</t>
+          <t>https://artportalen.se/Sighting/135493721</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135493721</v>
+        <v>89165399</v>
       </c>
       <c r="B11" t="n">
-        <v>93365</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687775</v>
+        <v>687510</v>
       </c>
       <c r="R11" t="n">
-        <v>6703504</v>
+        <v>6703240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,12 +1743,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,80 +1759,70 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>örtrik barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493721</t>
+          <t>https://artportalen.se/Sighting/89165399</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89165399</v>
+        <v>128945973</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>93223</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>5448</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687510</v>
+        <v>687775</v>
       </c>
       <c r="R12" t="n">
-        <v>6703240</v>
+        <v>6703527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,12 +1849,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,35 +1865,36 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165399</t>
+          <t>https://artportalen.se/Sighting/128945973</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128945973</v>
+        <v>111733128</v>
       </c>
       <c r="B13" t="n">
-        <v>93223</v>
+        <v>91409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,21 +1902,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5448</v>
+        <v>5741</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1940,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687775</v>
+        <v>687588</v>
       </c>
       <c r="R13" t="n">
-        <v>6703527</v>
+        <v>6703243</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,12 +1956,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,11 +1972,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2006,16 +1987,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945973</t>
+          <t>https://artportalen.se/Sighting/111733128</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111733128</v>
+        <v>89165391</v>
       </c>
       <c r="B14" t="n">
-        <v>91409</v>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,34 +2004,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687588</v>
+        <v>687591</v>
       </c>
       <c r="R14" t="n">
-        <v>6703243</v>
+        <v>6703322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,12 +2067,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,74 +2087,73 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111733128</t>
+          <t>https://artportalen.se/Sighting/89165391</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89165391</v>
+        <v>118536152</v>
       </c>
       <c r="B15" t="n">
-        <v>93233</v>
+        <v>57258</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>100065</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687591</v>
+        <v>687724</v>
       </c>
       <c r="R15" t="n">
-        <v>6703322</v>
+        <v>6703501</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,12 +2177,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,60 +2197,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165391</t>
+          <t>https://artportalen.se/Sighting/118536152</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118536152</v>
+        <v>14574479</v>
       </c>
       <c r="B16" t="n">
-        <v>57258</v>
+        <v>45049</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100065</v>
+        <v>102021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2298,12 +2284,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2329,44 +2315,50 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536152</t>
+          <t>https://artportalen.se/Sighting/14574479</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14574479</v>
+        <v>60343384</v>
       </c>
       <c r="B17" t="n">
-        <v>45049</v>
+        <v>57754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102021</v>
+        <v>102118</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2405,12 +2397,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Troligen från hygge några hundra meter västerut</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2436,38 +2443,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574479</t>
+          <t>https://artportalen.se/Sighting/60343384</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>60343384</v>
+        <v>14574465</v>
       </c>
       <c r="B18" t="n">
-        <v>57754</v>
+        <v>43251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102118</v>
+        <v>102923</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1760)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2475,11 +2482,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2518,27 +2523,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Troligen från hygge några hundra meter västerut</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,50 +2554,45 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60343384</t>
+          <t>https://artportalen.se/Sighting/14574465</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14574465</v>
+        <v>118536149</v>
       </c>
       <c r="B19" t="n">
-        <v>43251</v>
+        <v>58209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102923</v>
+        <v>102980</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2644,12 +2629,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2675,38 +2660,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574465</t>
+          <t>https://artportalen.se/Sighting/118536149</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118536149</v>
+        <v>118536096</v>
       </c>
       <c r="B20" t="n">
-        <v>58209</v>
+        <v>58439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102980</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2781,45 +2766,51 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536149</t>
+          <t>https://artportalen.se/Sighting/118536096</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118536096</v>
+        <v>14144885</v>
       </c>
       <c r="B21" t="n">
-        <v>58439</v>
+        <v>43219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103018</v>
+        <v>201028</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2856,12 +2847,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,6 +2863,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2887,16 +2883,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536096</t>
+          <t>https://artportalen.se/Sighting/14144885</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14144885</v>
+        <v>14144900</v>
       </c>
       <c r="B22" t="n">
-        <v>43219</v>
+        <v>43369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,21 +2900,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>201028</v>
+        <v>201078</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Frejas pärlemorfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Boloria freija</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Thunberg, 1791)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2929,7 +2925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>slag-/vattenhåvning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2968,12 +2964,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,16 +3000,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144885</t>
+          <t>https://artportalen.se/Sighting/14144900</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14144900</v>
+        <v>14411268</v>
       </c>
       <c r="B23" t="n">
-        <v>43369</v>
+        <v>43464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,21 +3017,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>201078</v>
+        <v>201116</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Frejas pärlemorfjäril</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Boloria freija</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Thunberg, 1791)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,12 +3081,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3101,11 +3097,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Tomt</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3121,38 +3112,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144900</t>
+          <t>https://artportalen.se/Sighting/14411268</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14411268</v>
+        <v>14574463</v>
       </c>
       <c r="B24" t="n">
-        <v>43464</v>
+        <v>43309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>201116</v>
+        <v>201146</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3161,11 +3152,6 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -3202,12 +3188,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3233,59 +3219,58 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14411268</t>
+          <t>https://artportalen.se/Sighting/14574463</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>14574463</v>
+        <v>89165388</v>
       </c>
       <c r="B25" t="n">
-        <v>43309</v>
+        <v>99141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>201146</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687724</v>
+        <v>687601</v>
       </c>
       <c r="R25" t="n">
-        <v>6703501</v>
+        <v>6703330</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3309,12 +3294,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3329,66 +3314,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574463</t>
+          <t>https://artportalen.se/Sighting/89165388</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89165388</v>
+        <v>121432317</v>
       </c>
       <c r="B26" t="n">
-        <v>99141</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219862</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687601</v>
+        <v>687770</v>
       </c>
       <c r="R26" t="n">
-        <v>6703330</v>
+        <v>6703509</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,12 +3400,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3435,31 +3420,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165388</t>
+          <t>https://artportalen.se/Sighting/121432317</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121432317</v>
+        <v>135493722</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687770</v>
+        <v>687734</v>
       </c>
       <c r="R27" t="n">
-        <v>6703509</v>
+        <v>6703536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,12 +3502,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3537,6 +3518,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3552,13 +3538,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432317</t>
+          <t>https://artportalen.se/Sighting/135493722</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135493722</v>
+        <v>135777737</v>
       </c>
       <c r="B28" t="n">
         <v>99276</v>
@@ -3593,13 +3579,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687734</v>
+        <v>687766</v>
       </c>
       <c r="R28" t="n">
-        <v>6703536</v>
+        <v>6703514</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3623,12 +3609,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3639,11 +3625,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>örtrik barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3659,16 +3640,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493722</t>
+          <t>https://artportalen.se/Sighting/135777737</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135777737</v>
+        <v>3871356</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>106414</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3676,37 +3657,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687766</v>
+        <v>687756</v>
       </c>
       <c r="R29" t="n">
-        <v>6703514</v>
+        <v>6703570</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3730,12 +3721,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,6 +3737,16 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>betad skog</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>mark</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3755,19 +3756,19 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135777737</t>
+          <t>https://artportalen.se/Sighting/3871356</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3871356</v>
+        <v>87114476</v>
       </c>
       <c r="B30" t="n">
         <v>106414</v>
@@ -3801,24 +3802,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal1, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687756</v>
+        <v>687607</v>
       </c>
       <c r="R30" t="n">
-        <v>6703570</v>
+        <v>6703660</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3842,12 +3841,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2020-07-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3856,17 +3860,13 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>betad skog</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>mark</t>
+          <t>Mittsträng på liten väg.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3871356</t>
+          <t>https://artportalen.se/Sighting/87114476</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>87114476</v>
+        <v>87966959</v>
       </c>
       <c r="B31" t="n">
-        <v>106414</v>
+        <v>106413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3923,22 +3923,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rosendal1, Upl</t>
+          <t>Rosendal (2), Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687607</v>
+        <v>687778</v>
       </c>
       <c r="R31" t="n">
-        <v>6703660</v>
+        <v>6703569</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3960,19 +3964,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C-Öst-0734</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
+          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3985,35 +3994,34 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Mittsträng på liten väg.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87114476</t>
+          <t>https://artportalen.se/Sighting/87966959</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>87966959</v>
+        <v>126492808</v>
       </c>
       <c r="B32" t="n">
-        <v>106413</v>
+        <v>106414</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4036,7 +4044,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4044,23 +4052,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rosendal (2), Upl</t>
+          <t>300 m N om Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687778</v>
+        <v>687618</v>
       </c>
       <c r="R32" t="n">
-        <v>6703569</v>
+        <v>6703661</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4085,24 +4089,14 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>C-Öst-0734</t>
-        </is>
-      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4118,77 +4112,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87966959</t>
+          <t>https://artportalen.se/Sighting/126492808</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126492808</v>
+        <v>4814079</v>
       </c>
       <c r="B33" t="n">
-        <v>106414</v>
+        <v>99879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221447</v>
+        <v>222361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>300 m N om Rosendal, Upl</t>
+          <t>Rosendal, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687618</v>
+        <v>687760</v>
       </c>
       <c r="R33" t="n">
-        <v>6703661</v>
+        <v>6703517</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4212,12 +4194,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2009-08-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Glänta i skog, betad fram till förra året</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4226,7 +4213,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4238,19 +4224,19 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126492808</t>
+          <t>https://artportalen.se/Sighting/4814079</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4814079</v>
+        <v>6984068</v>
       </c>
       <c r="B34" t="n">
         <v>99879</v>
@@ -4278,20 +4264,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rosendal, Gräsö, Upl</t>
+          <t>Rosendal, 200 m NNO om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687760</v>
+        <v>687796</v>
       </c>
       <c r="R34" t="n">
-        <v>6703517</v>
+        <v>6703570</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4315,17 +4312,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Glänta i skog, betad fram till förra året</t>
+          <t>Ny lokal för loppstarr på Gräsö</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4336,28 +4333,33 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark i skog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4814079</t>
+          <t>https://artportalen.se/Sighting/6984068</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6984068</v>
+        <v>6996375</v>
       </c>
       <c r="B35" t="n">
         <v>99879</v>
@@ -4385,28 +4387,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rosendal, 200 m NNO om, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687796</v>
+        <v>687741</v>
       </c>
       <c r="R35" t="n">
-        <v>6703570</v>
+        <v>6703554</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4433,17 +4424,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ny lokal för loppstarr på Gräsö</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4454,71 +4440,75 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark i skog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6984068</t>
+          <t>https://artportalen.se/Sighting/6996375</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6996375</v>
+        <v>6180132</v>
       </c>
       <c r="B36" t="n">
-        <v>99879</v>
+        <v>106417</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222361</v>
+        <v>224210</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Tidig fältgentiana</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Gentianella campestris var. suecica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Gräsö, Rosendal (1), Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687741</v>
+        <v>687781</v>
       </c>
       <c r="R36" t="n">
-        <v>6703554</v>
+        <v>6703580</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4543,14 +4533,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C-Öst-0707</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4565,24 +4565,28 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Floraväkterisamordn C-län</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Via Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6996375</t>
+          <t>https://artportalen.se/Sighting/6180132</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6180132</v>
+        <v>6181625</v>
       </c>
       <c r="B37" t="n">
         <v>106417</v>
@@ -4612,7 +4616,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4620,19 +4624,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gräsö, Rosendal (1), Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>687781</v>
+        <v>687797</v>
       </c>
       <c r="R37" t="n">
         <v>6703580</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4654,24 +4663,19 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>C-Öst-0707</t>
-        </is>
-      </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4686,145 +4690,20 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Floraväkterisamordn C-län</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Floraväkterisamordn C-län</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/6180132</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>6181625</v>
-      </c>
-      <c r="B38" t="n">
-        <v>106417</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>224210</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tidig fältgentiana</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Gentianella campestris var. suecica</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Rosendal, Upl</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>687797</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6703580</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Gräsö</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2008-07-02</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2008-07-02</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Maria Pettersson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Maria Pettersson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
-      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6181625</t>
         </is>
@@ -4868,7 +4747,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,32 +1034,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89165393</v>
+        <v>135402831</v>
       </c>
       <c r="B5" t="n">
-        <v>91680</v>
+        <v>91514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>720</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,19 +1069,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687584</v>
+        <v>687766</v>
       </c>
       <c r="R5" t="n">
-        <v>6703171</v>
+        <v>6703520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,12 +1108,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Troligtvis ett mycel med ringdiameter ca 9 m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,35 +1129,36 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165393</t>
+          <t>https://artportalen.se/Sighting/135402831</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80770115</v>
+        <v>89165393</v>
       </c>
       <c r="B6" t="n">
-        <v>87309</v>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1166,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100-300 m syd Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687668</v>
+        <v>687584</v>
       </c>
       <c r="R6" t="n">
-        <v>6703252</v>
+        <v>6703171</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1229,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-07</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,24 +1249,28 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770115</t>
+          <t>https://artportalen.se/Sighting/89165393</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80770116</v>
+        <v>80770115</v>
       </c>
       <c r="B7" t="n">
         <v>87309</v>
@@ -1286,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687675</v>
+        <v>687668</v>
       </c>
       <c r="R7" t="n">
-        <v>6703269</v>
+        <v>6703252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,51 +1366,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80770116</t>
+          <t>https://artportalen.se/Sighting/80770115</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121432323</v>
+        <v>80770116</v>
       </c>
       <c r="B8" t="n">
-        <v>93189</v>
+        <v>87309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>100-300 m syd Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687776</v>
+        <v>687675</v>
       </c>
       <c r="R8" t="n">
-        <v>6703519</v>
+        <v>6703269</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,12 +1437,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,13 +1468,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432323</t>
+          <t>https://artportalen.se/Sighting/80770116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128945974</v>
+        <v>121432323</v>
       </c>
       <c r="B9" t="n">
         <v>93189</v>
@@ -1490,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687781</v>
+        <v>687776</v>
       </c>
       <c r="R9" t="n">
-        <v>6703516</v>
+        <v>6703519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,12 +1539,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,11 +1555,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1556,16 +1570,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945974</t>
+          <t>https://artportalen.se/Sighting/121432323</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135493721</v>
+        <v>128945974</v>
       </c>
       <c r="B10" t="n">
-        <v>93365</v>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687775</v>
+        <v>687781</v>
       </c>
       <c r="R10" t="n">
-        <v>6703504</v>
+        <v>6703516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,12 +1641,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,7 +1660,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>örtrik barrskog</t>
+          <t>kalkbarrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1657,66 +1671,57 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493721</t>
+          <t>https://artportalen.se/Sighting/128945974</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89165399</v>
+        <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>93365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687510</v>
+        <v>687775</v>
       </c>
       <c r="R11" t="n">
-        <v>6703240</v>
+        <v>6703504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,70 +1764,80 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165399</t>
+          <t>https://artportalen.se/Sighting/135493721</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128945973</v>
+        <v>89165399</v>
       </c>
       <c r="B12" t="n">
-        <v>93223</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5448</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687775</v>
+        <v>687510</v>
       </c>
       <c r="R12" t="n">
-        <v>6703527</v>
+        <v>6703240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,12 +1864,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,36 +1880,35 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128945973</t>
+          <t>https://artportalen.se/Sighting/89165399</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111733128</v>
+        <v>128945973</v>
       </c>
       <c r="B13" t="n">
-        <v>91409</v>
+        <v>93223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,21 +1916,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5741</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1926,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687588</v>
+        <v>687775</v>
       </c>
       <c r="R13" t="n">
-        <v>6703243</v>
+        <v>6703527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,12 +1970,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,6 +1986,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1987,16 +2006,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111733128</t>
+          <t>https://artportalen.se/Sighting/128945973</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89165391</v>
+        <v>111733128</v>
       </c>
       <c r="B14" t="n">
-        <v>93233</v>
+        <v>91409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,43 +2023,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687591</v>
+        <v>687588</v>
       </c>
       <c r="R14" t="n">
-        <v>6703322</v>
+        <v>6703243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,12 +2077,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2087,73 +2097,74 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165391</t>
+          <t>https://artportalen.se/Sighting/111733128</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118536152</v>
+        <v>89165391</v>
       </c>
       <c r="B15" t="n">
-        <v>57258</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100065</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687724</v>
+        <v>687591</v>
       </c>
       <c r="R15" t="n">
-        <v>6703501</v>
+        <v>6703322</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2177,12 +2188,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,57 +2208,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536152</t>
+          <t>https://artportalen.se/Sighting/89165391</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14574479</v>
+        <v>118536152</v>
       </c>
       <c r="B16" t="n">
-        <v>45049</v>
+        <v>57258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102021</v>
+        <v>100065</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2284,12 +2298,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,50 +2329,44 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574479</t>
+          <t>https://artportalen.se/Sighting/118536152</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>60343384</v>
+        <v>14574479</v>
       </c>
       <c r="B17" t="n">
-        <v>57754</v>
+        <v>45049</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102118</v>
+        <v>102021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2397,27 +2405,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Troligen från hygge några hundra meter västerut</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,38 +2436,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60343384</t>
+          <t>https://artportalen.se/Sighting/14574479</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14574465</v>
+        <v>60343384</v>
       </c>
       <c r="B18" t="n">
-        <v>43251</v>
+        <v>57754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102923</v>
+        <v>102118</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2482,9 +2475,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2523,12 +2518,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-06-30</t>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Troligen från hygge några hundra meter västerut</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,45 +2564,50 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574465</t>
+          <t>https://artportalen.se/Sighting/60343384</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118536149</v>
+        <v>14574465</v>
       </c>
       <c r="B19" t="n">
-        <v>58209</v>
+        <v>43251</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102980</v>
+        <v>102923</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2629,12 +2644,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2010-06-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,38 +2675,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536149</t>
+          <t>https://artportalen.se/Sighting/14574465</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118536096</v>
+        <v>118536149</v>
       </c>
       <c r="B20" t="n">
-        <v>58439</v>
+        <v>58209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>102980</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2766,51 +2781,45 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118536096</t>
+          <t>https://artportalen.se/Sighting/118536149</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14144885</v>
+        <v>118536096</v>
       </c>
       <c r="B21" t="n">
-        <v>43219</v>
+        <v>58439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201028</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -2847,12 +2856,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2009-07-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,11 +2872,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Tomt</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2883,16 +2887,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144885</t>
+          <t>https://artportalen.se/Sighting/118536096</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14144900</v>
+        <v>14144885</v>
       </c>
       <c r="B22" t="n">
-        <v>43369</v>
+        <v>43219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2900,21 +2904,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>201078</v>
+        <v>201028</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Frejas pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Boloria freija</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Thunberg, 1791)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,7 +2929,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>slag-/vattenhåvning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2964,12 +2968,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2009-07-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,16 +3004,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14144900</t>
+          <t>https://artportalen.se/Sighting/14144885</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14411268</v>
+        <v>14144900</v>
       </c>
       <c r="B23" t="n">
-        <v>43464</v>
+        <v>43369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,21 +3021,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>201116</v>
+        <v>201078</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Frejas pärlemorfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Boloria freija</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Thunberg, 1791)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,12 +3085,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,6 +3101,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Tomt</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3112,38 +3121,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14411268</t>
+          <t>https://artportalen.se/Sighting/14144900</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14574463</v>
+        <v>14411268</v>
       </c>
       <c r="B24" t="n">
-        <v>43309</v>
+        <v>43464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>201146</v>
+        <v>201116</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3152,6 +3161,11 @@
           <t>imago/adult</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
@@ -3188,12 +3202,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2010-07-02</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3219,58 +3233,59 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14574463</t>
+          <t>https://artportalen.se/Sighting/14411268</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89165388</v>
+        <v>14574463</v>
       </c>
       <c r="B25" t="n">
-        <v>99141</v>
+        <v>43309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219862</v>
+        <v>201146</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rosendal Söderboda, Gräsö, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687601</v>
+        <v>687724</v>
       </c>
       <c r="R25" t="n">
-        <v>6703330</v>
+        <v>6703501</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3294,12 +3309,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2010-07-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3314,66 +3329,66 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89165388</t>
+          <t>https://artportalen.se/Sighting/14574463</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121432317</v>
+        <v>89165388</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>99141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal Söderboda, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687770</v>
+        <v>687601</v>
       </c>
       <c r="R26" t="n">
-        <v>6703509</v>
+        <v>6703330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,12 +3415,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,27 +3435,31 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121432317</t>
+          <t>https://artportalen.se/Sighting/89165388</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135493722</v>
+        <v>121432317</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3472,10 +3491,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687734</v>
+        <v>687770</v>
       </c>
       <c r="R27" t="n">
-        <v>6703536</v>
+        <v>6703509</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3502,12 +3521,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3518,11 +3537,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>örtrik barrskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3538,13 +3552,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493722</t>
+          <t>https://artportalen.se/Sighting/121432317</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135777737</v>
+        <v>135493722</v>
       </c>
       <c r="B28" t="n">
         <v>99276</v>
@@ -3579,13 +3593,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687766</v>
+        <v>687734</v>
       </c>
       <c r="R28" t="n">
-        <v>6703514</v>
+        <v>6703536</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3609,12 +3623,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,6 +3639,11 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>örtrik barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3640,16 +3659,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135777737</t>
+          <t>https://artportalen.se/Sighting/135493722</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3871356</v>
+        <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>106414</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,47 +3676,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221447</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687756</v>
+        <v>687766</v>
       </c>
       <c r="R29" t="n">
-        <v>6703570</v>
+        <v>6703514</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3721,12 +3730,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2005-07-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3737,16 +3746,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>betad skog</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>mark</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3756,19 +3755,19 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3871356</t>
+          <t>https://artportalen.se/Sighting/135777737</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>87114476</v>
+        <v>3871356</v>
       </c>
       <c r="B30" t="n">
         <v>106414</v>
@@ -3802,22 +3801,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rosendal1, Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687607</v>
+        <v>687756</v>
       </c>
       <c r="R30" t="n">
-        <v>6703660</v>
+        <v>6703570</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3841,17 +3842,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
+          <t>2005-07-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3860,13 +3856,17 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Mittsträng på liten väg.</t>
+          <t>betad skog</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>mark</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87114476</t>
+          <t>https://artportalen.se/Sighting/3871356</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>87966959</v>
+        <v>87114476</v>
       </c>
       <c r="B31" t="n">
-        <v>106413</v>
+        <v>106414</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3923,26 +3923,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rosendal (2), Upl</t>
+          <t>Rosendal1, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687778</v>
+        <v>687607</v>
       </c>
       <c r="R31" t="n">
-        <v>6703569</v>
+        <v>6703660</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3964,24 +3960,19 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>C-Öst-0734</t>
-        </is>
-      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
+          <t>Ej i blom än.  Ca 8 m in på vägen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3994,34 +3985,35 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Mittsträng på liten väg.</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87966959</t>
+          <t>https://artportalen.se/Sighting/87114476</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126492808</v>
+        <v>87966959</v>
       </c>
       <c r="B32" t="n">
-        <v>106414</v>
+        <v>106413</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4036,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4052,19 +4044,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>300 m N om Rosendal, Upl</t>
+          <t>Rosendal (2), Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687618</v>
+        <v>687778</v>
       </c>
       <c r="R32" t="n">
-        <v>6703661</v>
+        <v>6703569</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,14 +4085,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C-Öst-0734</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2020-08-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Återfunnen på lokalen efter att inte ha setts sedan 2014. I väktarlokalen är den upplagd som "tidig fältgentiana", vilket verkar felaktigt eftersom den blommade 22 augusti.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,65 +4118,77 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126492808</t>
+          <t>https://artportalen.se/Sighting/87966959</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4814079</v>
+        <v>126492808</v>
       </c>
       <c r="B33" t="n">
-        <v>99879</v>
+        <v>106414</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222361</v>
+        <v>221447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rosendal, Gräsö, Upl</t>
+          <t>300 m N om Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687760</v>
+        <v>687618</v>
       </c>
       <c r="R33" t="n">
-        <v>6703517</v>
+        <v>6703661</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4194,17 +4212,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2009-08-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Glänta i skog, betad fram till förra året</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4213,6 +4226,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4224,19 +4238,19 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4814079</t>
+          <t>https://artportalen.se/Sighting/126492808</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6984068</v>
+        <v>4814079</v>
       </c>
       <c r="B34" t="n">
         <v>99879</v>
@@ -4264,31 +4278,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rosendal, 200 m NNO om, Upl</t>
+          <t>Rosendal, Gräsö, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687796</v>
+        <v>687760</v>
       </c>
       <c r="R34" t="n">
-        <v>6703570</v>
+        <v>6703517</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4312,17 +4315,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2013-07-06</t>
+          <t>2009-08-09</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ny lokal för loppstarr på Gräsö</t>
+          <t>Glänta i skog, betad fram till förra året</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4333,33 +4336,28 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark i skog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6984068</t>
+          <t>https://artportalen.se/Sighting/4814079</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6996375</v>
+        <v>6984068</v>
       </c>
       <c r="B35" t="n">
         <v>99879</v>
@@ -4387,17 +4385,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Rosendal, 200 m NNO om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687741</v>
+        <v>687796</v>
       </c>
       <c r="R35" t="n">
-        <v>6703554</v>
+        <v>6703570</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4424,12 +4433,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2013-07-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2013-07-31</t>
+          <t>2013-07-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ny lokal för loppstarr på Gräsö</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4440,75 +4454,71 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark i skog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Ingvar Sundh</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6996375</t>
+          <t>https://artportalen.se/Sighting/6984068</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6180132</v>
+        <v>6996375</v>
       </c>
       <c r="B36" t="n">
-        <v>106417</v>
+        <v>99879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>224210</v>
+        <v>222361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gräsö, Rosendal (1), Upl</t>
+          <t>Rosendal, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687781</v>
+        <v>687741</v>
       </c>
       <c r="R36" t="n">
-        <v>6703580</v>
+        <v>6703554</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,24 +4543,14 @@
           <t>Gräsö</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>C-Öst-0707</t>
-        </is>
-      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4565,28 +4565,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Floraväkterisamordn C-län</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Floraväkterisamordn C-län</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6180132</t>
+          <t>https://artportalen.se/Sighting/6996375</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6181625</v>
+        <v>6180132</v>
       </c>
       <c r="B37" t="n">
         <v>106417</v>
@@ -4616,7 +4612,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4624,24 +4620,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rosendal, Upl</t>
+          <t>Gräsö, Rosendal (1), Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>687797</v>
+        <v>687781</v>
       </c>
       <c r="R37" t="n">
         <v>6703580</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4663,19 +4654,24 @@
           <t>Gräsö</t>
         </is>
       </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C-Öst-0707</t>
+        </is>
+      </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2008-07-02</t>
+          <t>2005-12-31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+          <t>6703455-1643555 (100m) - 13 ex, 6703655-1643355 - 1 ex Thomas Troschke</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,20 +4686,145 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
+          <t>Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6180132</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6181625</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Rosendal, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>687797</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6703580</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2008-07-02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Betesmark. Inventeringen genomförd för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Uppsala län.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Maria Pettersson</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6181625</t>
         </is>
@@ -4747,6 +4868,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>135402831</v>
       </c>
       <c r="B5" t="n">
-        <v>91514</v>
+        <v>91516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>135493722</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>135493722</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93382</v>
+        <v>93383</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93383</v>
+        <v>93389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135777737</v>
       </c>
       <c r="B29" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93404</v>
+        <v>93417</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2026 artfynd.xlsx
+++ b/artfynd/A 1101-2026 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135493721</v>
       </c>
       <c r="B11" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
